--- a/FM-MN-07_LATHE-01.xlsx
+++ b/FM-MN-07_LATHE-01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\Maintenance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A91CD31-1295-4D26-A86D-34787A6C4D90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57BE8684-4621-4135-81FE-E0985A4E13B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CD1D512E-4DC4-4013-847A-2CE399DEA74A}"/>
   </bookViews>
@@ -312,29 +312,11 @@
   <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -361,41 +343,61 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="4"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="4" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="4"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="4" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1449,999 +1451,913 @@
     <col min="16131" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" s="26" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A1" s="31" t="s">
+    <row r="1" spans="1:33" s="15" customFormat="1" ht="25.5" customHeight="1">
+      <c r="A1" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="31"/>
-      <c r="R1" s="31"/>
-      <c r="S1" s="31"/>
-      <c r="T1" s="31"/>
-      <c r="U1" s="31"/>
-      <c r="V1" s="31"/>
-      <c r="W1" s="31"/>
-      <c r="X1" s="31"/>
-      <c r="Y1" s="31"/>
-      <c r="Z1" s="31"/>
-      <c r="AA1" s="31"/>
-      <c r="AB1" s="30" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
+      <c r="N1" s="23"/>
+      <c r="O1" s="23"/>
+      <c r="P1" s="23"/>
+      <c r="Q1" s="23"/>
+      <c r="R1" s="23"/>
+      <c r="S1" s="23"/>
+      <c r="T1" s="23"/>
+      <c r="U1" s="23"/>
+      <c r="V1" s="23"/>
+      <c r="W1" s="23"/>
+      <c r="X1" s="23"/>
+      <c r="Y1" s="23"/>
+      <c r="Z1" s="23"/>
+      <c r="AA1" s="23"/>
+      <c r="AB1" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="AC1" s="30"/>
-      <c r="AD1" s="30"/>
-      <c r="AE1" s="30"/>
-      <c r="AF1" s="30"/>
-      <c r="AG1" s="30"/>
+      <c r="AC1" s="24"/>
+      <c r="AD1" s="24"/>
+      <c r="AE1" s="24"/>
+      <c r="AF1" s="24"/>
+      <c r="AG1" s="24"/>
     </row>
-    <row r="2" spans="1:33" s="26" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A2" s="31"/>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="31"/>
-      <c r="K2" s="31"/>
-      <c r="L2" s="31"/>
-      <c r="M2" s="31"/>
-      <c r="N2" s="31"/>
-      <c r="O2" s="31"/>
-      <c r="P2" s="31"/>
-      <c r="Q2" s="31"/>
-      <c r="R2" s="31"/>
-      <c r="S2" s="31"/>
-      <c r="T2" s="31"/>
-      <c r="U2" s="31"/>
-      <c r="V2" s="31"/>
-      <c r="W2" s="31"/>
-      <c r="X2" s="31"/>
-      <c r="Y2" s="31"/>
-      <c r="Z2" s="31"/>
-      <c r="AA2" s="31"/>
-      <c r="AB2" s="30" t="s">
+    <row r="2" spans="1:33" s="15" customFormat="1" ht="25.5" customHeight="1">
+      <c r="A2" s="23"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="23"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
+      <c r="S2" s="23"/>
+      <c r="T2" s="23"/>
+      <c r="U2" s="23"/>
+      <c r="V2" s="23"/>
+      <c r="W2" s="23"/>
+      <c r="X2" s="23"/>
+      <c r="Y2" s="23"/>
+      <c r="Z2" s="23"/>
+      <c r="AA2" s="23"/>
+      <c r="AB2" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="AC2" s="30"/>
-      <c r="AD2" s="30"/>
-      <c r="AE2" s="30"/>
-      <c r="AF2" s="30"/>
-      <c r="AG2" s="30"/>
+      <c r="AC2" s="24"/>
+      <c r="AD2" s="24"/>
+      <c r="AE2" s="24"/>
+      <c r="AF2" s="24"/>
+      <c r="AG2" s="24"/>
     </row>
-    <row r="3" spans="1:33" s="26" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A3" s="29"/>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="27"/>
-      <c r="H3" s="27"/>
-      <c r="I3" s="27"/>
-      <c r="J3" s="27"/>
-      <c r="K3" s="27"/>
-      <c r="L3" s="27"/>
-      <c r="M3" s="27"/>
-      <c r="N3" s="27"/>
-      <c r="O3" s="27"/>
-      <c r="P3" s="27"/>
-      <c r="Q3" s="27"/>
-      <c r="R3" s="27"/>
-      <c r="S3" s="27"/>
-      <c r="T3" s="27"/>
-      <c r="U3" s="27"/>
-      <c r="V3" s="27"/>
-      <c r="W3" s="27"/>
-      <c r="X3" s="27"/>
-      <c r="Y3" s="27"/>
-      <c r="Z3" s="27"/>
-      <c r="AA3" s="27"/>
-      <c r="AB3" s="27"/>
-      <c r="AC3" s="27"/>
-      <c r="AD3" s="27"/>
-      <c r="AE3" s="27"/>
-      <c r="AF3" s="27"/>
-      <c r="AG3" s="27"/>
+    <row r="3" spans="1:33" s="15" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A3" s="18"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="16"/>
+      <c r="L3" s="16"/>
+      <c r="M3" s="16"/>
+      <c r="N3" s="16"/>
+      <c r="O3" s="16"/>
+      <c r="P3" s="16"/>
+      <c r="Q3" s="16"/>
+      <c r="R3" s="16"/>
+      <c r="S3" s="16"/>
+      <c r="T3" s="16"/>
+      <c r="U3" s="16"/>
+      <c r="V3" s="16"/>
+      <c r="W3" s="16"/>
+      <c r="X3" s="16"/>
+      <c r="Y3" s="16"/>
+      <c r="Z3" s="16"/>
+      <c r="AA3" s="16"/>
+      <c r="AB3" s="16"/>
+      <c r="AC3" s="16"/>
+      <c r="AD3" s="16"/>
+      <c r="AE3" s="16"/>
+      <c r="AF3" s="16"/>
+      <c r="AG3" s="16"/>
     </row>
-    <row r="4" spans="1:33" s="19" customFormat="1" ht="18" customHeight="1">
+    <row r="4" spans="1:33" s="13" customFormat="1" ht="18" customHeight="1">
       <c r="A4" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="23" t="s">
+      <c r="C4" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="23"/>
-      <c r="K4" s="23"/>
-      <c r="L4" s="23"/>
-      <c r="M4" s="23"/>
-      <c r="N4" s="23"/>
-      <c r="O4" s="23"/>
-      <c r="P4" s="23"/>
-      <c r="Q4" s="23"/>
-      <c r="R4" s="23"/>
-      <c r="S4" s="23"/>
-      <c r="T4" s="23"/>
-      <c r="U4" s="23"/>
-      <c r="V4" s="23"/>
-      <c r="W4" s="23"/>
-      <c r="X4" s="23"/>
-      <c r="Y4" s="23"/>
-      <c r="Z4" s="23"/>
-      <c r="AA4" s="23"/>
-      <c r="AB4" s="23"/>
-      <c r="AC4" s="23"/>
-      <c r="AD4" s="23"/>
-      <c r="AE4" s="23"/>
-      <c r="AF4" s="23"/>
-      <c r="AG4" s="23"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
+      <c r="K4" s="29"/>
+      <c r="L4" s="29"/>
+      <c r="M4" s="29"/>
+      <c r="N4" s="29"/>
+      <c r="O4" s="29"/>
+      <c r="P4" s="29"/>
+      <c r="Q4" s="29"/>
+      <c r="R4" s="29"/>
+      <c r="S4" s="29"/>
+      <c r="T4" s="29"/>
+      <c r="U4" s="29"/>
+      <c r="V4" s="29"/>
+      <c r="W4" s="29"/>
+      <c r="X4" s="29"/>
+      <c r="Y4" s="29"/>
+      <c r="Z4" s="29"/>
+      <c r="AA4" s="29"/>
+      <c r="AB4" s="29"/>
+      <c r="AC4" s="29"/>
+      <c r="AD4" s="29"/>
+      <c r="AE4" s="29"/>
+      <c r="AF4" s="29"/>
+      <c r="AG4" s="29"/>
     </row>
-    <row r="5" spans="1:33" s="19" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A5" s="22"/>
-      <c r="B5" s="21"/>
-      <c r="C5" s="20">
+    <row r="5" spans="1:33" s="13" customFormat="1" ht="13.5" customHeight="1">
+      <c r="A5" s="26"/>
+      <c r="B5" s="28"/>
+      <c r="C5" s="14">
         <v>1</v>
       </c>
-      <c r="D5" s="20">
+      <c r="D5" s="14">
         <v>2</v>
       </c>
-      <c r="E5" s="20">
+      <c r="E5" s="14">
         <v>3</v>
       </c>
-      <c r="F5" s="20">
+      <c r="F5" s="14">
         <v>4</v>
       </c>
-      <c r="G5" s="20">
+      <c r="G5" s="14">
         <v>5</v>
       </c>
-      <c r="H5" s="20">
+      <c r="H5" s="14">
         <v>6</v>
       </c>
-      <c r="I5" s="20">
+      <c r="I5" s="14">
         <v>7</v>
       </c>
-      <c r="J5" s="20">
+      <c r="J5" s="14">
         <v>8</v>
       </c>
-      <c r="K5" s="20">
+      <c r="K5" s="14">
         <v>9</v>
       </c>
-      <c r="L5" s="20">
+      <c r="L5" s="14">
         <v>10</v>
       </c>
-      <c r="M5" s="20">
+      <c r="M5" s="14">
         <v>11</v>
       </c>
-      <c r="N5" s="20">
+      <c r="N5" s="14">
         <v>12</v>
       </c>
-      <c r="O5" s="20">
+      <c r="O5" s="14">
         <v>13</v>
       </c>
-      <c r="P5" s="20">
+      <c r="P5" s="14">
         <v>14</v>
       </c>
-      <c r="Q5" s="20">
+      <c r="Q5" s="14">
         <v>15</v>
       </c>
-      <c r="R5" s="20">
+      <c r="R5" s="14">
         <v>16</v>
       </c>
-      <c r="S5" s="20">
+      <c r="S5" s="14">
         <v>17</v>
       </c>
-      <c r="T5" s="20">
+      <c r="T5" s="14">
         <v>18</v>
       </c>
-      <c r="U5" s="20">
+      <c r="U5" s="14">
         <v>19</v>
       </c>
-      <c r="V5" s="20">
+      <c r="V5" s="14">
         <v>20</v>
       </c>
-      <c r="W5" s="20">
+      <c r="W5" s="14">
         <v>21</v>
       </c>
-      <c r="X5" s="20">
+      <c r="X5" s="14">
         <v>22</v>
       </c>
-      <c r="Y5" s="20">
+      <c r="Y5" s="14">
         <v>23</v>
       </c>
-      <c r="Z5" s="20">
+      <c r="Z5" s="14">
         <v>24</v>
       </c>
-      <c r="AA5" s="20">
+      <c r="AA5" s="14">
         <v>25</v>
       </c>
-      <c r="AB5" s="20">
+      <c r="AB5" s="14">
         <v>26</v>
       </c>
-      <c r="AC5" s="20">
+      <c r="AC5" s="14">
         <v>27</v>
       </c>
-      <c r="AD5" s="20">
+      <c r="AD5" s="14">
         <v>28</v>
       </c>
-      <c r="AE5" s="20">
+      <c r="AE5" s="14">
         <v>29</v>
       </c>
-      <c r="AF5" s="20">
+      <c r="AF5" s="14">
         <v>30</v>
       </c>
-      <c r="AG5" s="20">
+      <c r="AG5" s="14">
         <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:33" ht="18" customHeight="1">
-      <c r="A6" s="15">
+      <c r="A6" s="9">
         <v>1</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="13"/>
-      <c r="N6" s="13"/>
-      <c r="O6" s="13"/>
-      <c r="P6" s="13"/>
-      <c r="Q6" s="13"/>
-      <c r="R6" s="13"/>
-      <c r="S6" s="13"/>
-      <c r="T6" s="13"/>
-      <c r="U6" s="13"/>
-      <c r="V6" s="13"/>
-      <c r="W6" s="13"/>
-      <c r="X6" s="13"/>
-      <c r="Y6" s="13"/>
-      <c r="Z6" s="13"/>
-      <c r="AA6" s="13"/>
-      <c r="AB6" s="13"/>
-      <c r="AC6" s="13"/>
-      <c r="AD6" s="13"/>
-      <c r="AE6" s="13"/>
-      <c r="AF6" s="13"/>
-      <c r="AG6" s="13"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7"/>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7"/>
+      <c r="U6" s="7"/>
+      <c r="V6" s="7"/>
+      <c r="W6" s="7"/>
+      <c r="X6" s="7"/>
+      <c r="Y6" s="7"/>
+      <c r="Z6" s="7"/>
+      <c r="AA6" s="7"/>
+      <c r="AB6" s="7"/>
+      <c r="AC6" s="7"/>
+      <c r="AD6" s="7"/>
+      <c r="AE6" s="7"/>
+      <c r="AF6" s="7"/>
+      <c r="AG6" s="7"/>
     </row>
     <row r="7" spans="1:33" ht="18" customHeight="1">
-      <c r="A7" s="15">
+      <c r="A7" s="9">
         <v>2</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
-      <c r="L7" s="13"/>
-      <c r="M7" s="13"/>
-      <c r="N7" s="13"/>
-      <c r="O7" s="13"/>
-      <c r="P7" s="13"/>
-      <c r="Q7" s="13"/>
-      <c r="R7" s="13"/>
-      <c r="S7" s="13"/>
-      <c r="T7" s="13"/>
-      <c r="U7" s="13"/>
-      <c r="V7" s="13"/>
-      <c r="W7" s="13"/>
-      <c r="X7" s="13"/>
-      <c r="Y7" s="13"/>
-      <c r="Z7" s="13"/>
-      <c r="AA7" s="13"/>
-      <c r="AB7" s="13"/>
-      <c r="AC7" s="13"/>
-      <c r="AD7" s="13"/>
-      <c r="AE7" s="13"/>
-      <c r="AF7" s="13"/>
-      <c r="AG7" s="13"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+      <c r="O7" s="7"/>
+      <c r="P7" s="7"/>
+      <c r="Q7" s="7"/>
+      <c r="R7" s="7"/>
+      <c r="S7" s="7"/>
+      <c r="T7" s="7"/>
+      <c r="U7" s="7"/>
+      <c r="V7" s="7"/>
+      <c r="W7" s="7"/>
+      <c r="X7" s="7"/>
+      <c r="Y7" s="7"/>
+      <c r="Z7" s="7"/>
+      <c r="AA7" s="7"/>
+      <c r="AB7" s="7"/>
+      <c r="AC7" s="7"/>
+      <c r="AD7" s="7"/>
+      <c r="AE7" s="7"/>
+      <c r="AF7" s="7"/>
+      <c r="AG7" s="7"/>
     </row>
     <row r="8" spans="1:33" ht="18" customHeight="1">
-      <c r="A8" s="15">
+      <c r="A8" s="9">
         <v>3</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="13"/>
-      <c r="M8" s="13"/>
-      <c r="N8" s="13"/>
-      <c r="O8" s="13"/>
-      <c r="P8" s="13"/>
-      <c r="Q8" s="13"/>
-      <c r="R8" s="13"/>
-      <c r="S8" s="13"/>
-      <c r="T8" s="13"/>
-      <c r="U8" s="13"/>
-      <c r="V8" s="13"/>
-      <c r="W8" s="13"/>
-      <c r="X8" s="13"/>
-      <c r="Y8" s="13"/>
-      <c r="Z8" s="13"/>
-      <c r="AA8" s="13"/>
-      <c r="AB8" s="13"/>
-      <c r="AC8" s="13"/>
-      <c r="AD8" s="13"/>
-      <c r="AE8" s="13"/>
-      <c r="AF8" s="13"/>
-      <c r="AG8" s="13"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
+      <c r="O8" s="7"/>
+      <c r="P8" s="7"/>
+      <c r="Q8" s="7"/>
+      <c r="R8" s="7"/>
+      <c r="S8" s="7"/>
+      <c r="T8" s="7"/>
+      <c r="U8" s="7"/>
+      <c r="V8" s="7"/>
+      <c r="W8" s="7"/>
+      <c r="X8" s="7"/>
+      <c r="Y8" s="7"/>
+      <c r="Z8" s="7"/>
+      <c r="AA8" s="7"/>
+      <c r="AB8" s="7"/>
+      <c r="AC8" s="7"/>
+      <c r="AD8" s="7"/>
+      <c r="AE8" s="7"/>
+      <c r="AF8" s="7"/>
+      <c r="AG8" s="7"/>
     </row>
     <row r="9" spans="1:33" ht="18" customHeight="1">
-      <c r="A9" s="15">
+      <c r="A9" s="9">
         <v>4</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="13"/>
-      <c r="M9" s="13"/>
-      <c r="N9" s="13"/>
-      <c r="O9" s="13"/>
-      <c r="P9" s="13"/>
-      <c r="Q9" s="13"/>
-      <c r="R9" s="13"/>
-      <c r="S9" s="13"/>
-      <c r="T9" s="13"/>
-      <c r="U9" s="13"/>
-      <c r="V9" s="13"/>
-      <c r="W9" s="13"/>
-      <c r="X9" s="13"/>
-      <c r="Y9" s="13"/>
-      <c r="Z9" s="13"/>
-      <c r="AA9" s="13"/>
-      <c r="AB9" s="13"/>
-      <c r="AC9" s="13"/>
-      <c r="AD9" s="13"/>
-      <c r="AE9" s="13"/>
-      <c r="AF9" s="13"/>
-      <c r="AG9" s="13"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
+      <c r="O9" s="7"/>
+      <c r="P9" s="7"/>
+      <c r="Q9" s="7"/>
+      <c r="R9" s="7"/>
+      <c r="S9" s="7"/>
+      <c r="T9" s="7"/>
+      <c r="U9" s="7"/>
+      <c r="V9" s="7"/>
+      <c r="W9" s="7"/>
+      <c r="X9" s="7"/>
+      <c r="Y9" s="7"/>
+      <c r="Z9" s="7"/>
+      <c r="AA9" s="7"/>
+      <c r="AB9" s="7"/>
+      <c r="AC9" s="7"/>
+      <c r="AD9" s="7"/>
+      <c r="AE9" s="7"/>
+      <c r="AF9" s="7"/>
+      <c r="AG9" s="7"/>
     </row>
     <row r="10" spans="1:33" ht="18" customHeight="1">
-      <c r="A10" s="15">
+      <c r="A10" s="9">
         <v>5</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13"/>
-      <c r="L10" s="13"/>
-      <c r="M10" s="13"/>
-      <c r="N10" s="13"/>
-      <c r="O10" s="13"/>
-      <c r="P10" s="13"/>
-      <c r="Q10" s="13"/>
-      <c r="R10" s="13"/>
-      <c r="S10" s="13"/>
-      <c r="T10" s="13"/>
-      <c r="U10" s="13"/>
-      <c r="V10" s="13"/>
-      <c r="W10" s="13"/>
-      <c r="X10" s="13"/>
-      <c r="Y10" s="13"/>
-      <c r="Z10" s="13"/>
-      <c r="AA10" s="13"/>
-      <c r="AB10" s="13"/>
-      <c r="AC10" s="13"/>
-      <c r="AD10" s="13"/>
-      <c r="AE10" s="13"/>
-      <c r="AF10" s="13"/>
-      <c r="AG10" s="13"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7"/>
+      <c r="O10" s="7"/>
+      <c r="P10" s="7"/>
+      <c r="Q10" s="7"/>
+      <c r="R10" s="7"/>
+      <c r="S10" s="7"/>
+      <c r="T10" s="7"/>
+      <c r="U10" s="7"/>
+      <c r="V10" s="7"/>
+      <c r="W10" s="7"/>
+      <c r="X10" s="7"/>
+      <c r="Y10" s="7"/>
+      <c r="Z10" s="7"/>
+      <c r="AA10" s="7"/>
+      <c r="AB10" s="7"/>
+      <c r="AC10" s="7"/>
+      <c r="AD10" s="7"/>
+      <c r="AE10" s="7"/>
+      <c r="AF10" s="7"/>
+      <c r="AG10" s="7"/>
     </row>
     <row r="11" spans="1:33" ht="18" customHeight="1">
-      <c r="A11" s="15">
+      <c r="A11" s="9">
         <v>6</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="13"/>
-      <c r="M11" s="13"/>
-      <c r="N11" s="13"/>
-      <c r="O11" s="13"/>
-      <c r="P11" s="13"/>
-      <c r="Q11" s="13"/>
-      <c r="R11" s="13"/>
-      <c r="S11" s="13"/>
-      <c r="T11" s="13"/>
-      <c r="U11" s="13"/>
-      <c r="V11" s="13"/>
-      <c r="W11" s="13"/>
-      <c r="X11" s="13"/>
-      <c r="Y11" s="13"/>
-      <c r="Z11" s="13"/>
-      <c r="AA11" s="13"/>
-      <c r="AB11" s="13"/>
-      <c r="AC11" s="13"/>
-      <c r="AD11" s="13"/>
-      <c r="AE11" s="13"/>
-      <c r="AF11" s="13"/>
-      <c r="AG11" s="13"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="7"/>
+      <c r="O11" s="7"/>
+      <c r="P11" s="7"/>
+      <c r="Q11" s="7"/>
+      <c r="R11" s="7"/>
+      <c r="S11" s="7"/>
+      <c r="T11" s="7"/>
+      <c r="U11" s="7"/>
+      <c r="V11" s="7"/>
+      <c r="W11" s="7"/>
+      <c r="X11" s="7"/>
+      <c r="Y11" s="7"/>
+      <c r="Z11" s="7"/>
+      <c r="AA11" s="7"/>
+      <c r="AB11" s="7"/>
+      <c r="AC11" s="7"/>
+      <c r="AD11" s="7"/>
+      <c r="AE11" s="7"/>
+      <c r="AF11" s="7"/>
+      <c r="AG11" s="7"/>
     </row>
     <row r="12" spans="1:33" ht="18" customHeight="1">
-      <c r="A12" s="34">
+      <c r="A12" s="20">
         <v>7</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="17"/>
-      <c r="J12" s="17"/>
-      <c r="K12" s="17"/>
-      <c r="L12" s="17"/>
-      <c r="M12" s="17"/>
-      <c r="N12" s="17"/>
-      <c r="O12" s="17"/>
-      <c r="P12" s="17"/>
-      <c r="Q12" s="17"/>
-      <c r="R12" s="17"/>
-      <c r="S12" s="17"/>
-      <c r="T12" s="17"/>
-      <c r="U12" s="17"/>
-      <c r="V12" s="17"/>
-      <c r="W12" s="17"/>
-      <c r="X12" s="17"/>
-      <c r="Y12" s="17"/>
-      <c r="Z12" s="17"/>
-      <c r="AA12" s="17"/>
-      <c r="AB12" s="17"/>
-      <c r="AC12" s="17"/>
-      <c r="AD12" s="17"/>
-      <c r="AE12" s="17"/>
-      <c r="AF12" s="17"/>
-      <c r="AG12" s="17"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="11"/>
+      <c r="N12" s="11"/>
+      <c r="O12" s="11"/>
+      <c r="P12" s="11"/>
+      <c r="Q12" s="11"/>
+      <c r="R12" s="11"/>
+      <c r="S12" s="11"/>
+      <c r="T12" s="11"/>
+      <c r="U12" s="11"/>
+      <c r="V12" s="11"/>
+      <c r="W12" s="11"/>
+      <c r="X12" s="11"/>
+      <c r="Y12" s="11"/>
+      <c r="Z12" s="11"/>
+      <c r="AA12" s="11"/>
+      <c r="AB12" s="11"/>
+      <c r="AC12" s="11"/>
+      <c r="AD12" s="11"/>
+      <c r="AE12" s="11"/>
+      <c r="AF12" s="11"/>
+      <c r="AG12" s="11"/>
     </row>
     <row r="13" spans="1:33" ht="18" customHeight="1">
-      <c r="A13" s="15">
+      <c r="A13" s="9">
         <v>8</v>
       </c>
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="13"/>
-      <c r="K13" s="13"/>
-      <c r="L13" s="13"/>
-      <c r="M13" s="13"/>
-      <c r="N13" s="13"/>
-      <c r="O13" s="13"/>
-      <c r="P13" s="13"/>
-      <c r="Q13" s="13"/>
-      <c r="R13" s="13"/>
-      <c r="S13" s="13"/>
-      <c r="T13" s="13"/>
-      <c r="U13" s="13"/>
-      <c r="V13" s="13"/>
-      <c r="W13" s="13"/>
-      <c r="X13" s="13"/>
-      <c r="Y13" s="13"/>
-      <c r="Z13" s="13"/>
-      <c r="AA13" s="13"/>
-      <c r="AB13" s="13"/>
-      <c r="AC13" s="13"/>
-      <c r="AD13" s="13"/>
-      <c r="AE13" s="13"/>
-      <c r="AF13" s="13"/>
-      <c r="AG13" s="13"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7"/>
+      <c r="O13" s="7"/>
+      <c r="P13" s="7"/>
+      <c r="Q13" s="7"/>
+      <c r="R13" s="7"/>
+      <c r="S13" s="7"/>
+      <c r="T13" s="7"/>
+      <c r="U13" s="7"/>
+      <c r="V13" s="7"/>
+      <c r="W13" s="7"/>
+      <c r="X13" s="7"/>
+      <c r="Y13" s="7"/>
+      <c r="Z13" s="7"/>
+      <c r="AA13" s="7"/>
+      <c r="AB13" s="7"/>
+      <c r="AC13" s="7"/>
+      <c r="AD13" s="7"/>
+      <c r="AE13" s="7"/>
+      <c r="AF13" s="7"/>
+      <c r="AG13" s="7"/>
     </row>
     <row r="14" spans="1:33" ht="18" customHeight="1">
-      <c r="A14" s="15">
+      <c r="A14" s="9">
         <v>9</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="13"/>
-      <c r="K14" s="13"/>
-      <c r="L14" s="13"/>
-      <c r="M14" s="13"/>
-      <c r="N14" s="13"/>
-      <c r="O14" s="13"/>
-      <c r="P14" s="13"/>
-      <c r="Q14" s="13"/>
-      <c r="R14" s="13"/>
-      <c r="S14" s="13"/>
-      <c r="T14" s="13"/>
-      <c r="U14" s="13"/>
-      <c r="V14" s="13"/>
-      <c r="W14" s="13"/>
-      <c r="X14" s="13"/>
-      <c r="Y14" s="13"/>
-      <c r="Z14" s="13"/>
-      <c r="AA14" s="13"/>
-      <c r="AB14" s="13"/>
-      <c r="AC14" s="13"/>
-      <c r="AD14" s="13"/>
-      <c r="AE14" s="13"/>
-      <c r="AF14" s="13"/>
-      <c r="AG14" s="13"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="7"/>
+      <c r="O14" s="7"/>
+      <c r="P14" s="7"/>
+      <c r="Q14" s="7"/>
+      <c r="R14" s="7"/>
+      <c r="S14" s="7"/>
+      <c r="T14" s="7"/>
+      <c r="U14" s="7"/>
+      <c r="V14" s="7"/>
+      <c r="W14" s="7"/>
+      <c r="X14" s="7"/>
+      <c r="Y14" s="7"/>
+      <c r="Z14" s="7"/>
+      <c r="AA14" s="7"/>
+      <c r="AB14" s="7"/>
+      <c r="AC14" s="7"/>
+      <c r="AD14" s="7"/>
+      <c r="AE14" s="7"/>
+      <c r="AF14" s="7"/>
+      <c r="AG14" s="7"/>
     </row>
     <row r="15" spans="1:33" ht="18" customHeight="1">
-      <c r="A15" s="15">
+      <c r="A15" s="9">
         <v>10</v>
       </c>
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="13"/>
-      <c r="L15" s="13"/>
-      <c r="M15" s="13"/>
-      <c r="N15" s="13"/>
-      <c r="O15" s="13"/>
-      <c r="P15" s="13"/>
-      <c r="Q15" s="13"/>
-      <c r="R15" s="13"/>
-      <c r="S15" s="13"/>
-      <c r="T15" s="13"/>
-      <c r="U15" s="13"/>
-      <c r="V15" s="13"/>
-      <c r="W15" s="13"/>
-      <c r="X15" s="13"/>
-      <c r="Y15" s="13"/>
-      <c r="Z15" s="13"/>
-      <c r="AA15" s="13"/>
-      <c r="AB15" s="13"/>
-      <c r="AC15" s="13"/>
-      <c r="AD15" s="13"/>
-      <c r="AE15" s="13"/>
-      <c r="AF15" s="13"/>
-      <c r="AG15" s="13"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="7"/>
+      <c r="O15" s="7"/>
+      <c r="P15" s="7"/>
+      <c r="Q15" s="7"/>
+      <c r="R15" s="7"/>
+      <c r="S15" s="7"/>
+      <c r="T15" s="7"/>
+      <c r="U15" s="7"/>
+      <c r="V15" s="7"/>
+      <c r="W15" s="7"/>
+      <c r="X15" s="7"/>
+      <c r="Y15" s="7"/>
+      <c r="Z15" s="7"/>
+      <c r="AA15" s="7"/>
+      <c r="AB15" s="7"/>
+      <c r="AC15" s="7"/>
+      <c r="AD15" s="7"/>
+      <c r="AE15" s="7"/>
+      <c r="AF15" s="7"/>
+      <c r="AG15" s="7"/>
     </row>
     <row r="16" spans="1:33" ht="18" customHeight="1">
-      <c r="A16" s="15">
+      <c r="A16" s="9">
         <v>11</v>
       </c>
-      <c r="B16" s="14" t="s">
+      <c r="B16" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13"/>
-      <c r="I16" s="13"/>
-      <c r="J16" s="13"/>
-      <c r="K16" s="13"/>
-      <c r="L16" s="13"/>
-      <c r="M16" s="13"/>
-      <c r="N16" s="13"/>
-      <c r="O16" s="13"/>
-      <c r="P16" s="13"/>
-      <c r="Q16" s="13"/>
-      <c r="R16" s="13"/>
-      <c r="S16" s="13"/>
-      <c r="T16" s="13"/>
-      <c r="U16" s="13"/>
-      <c r="V16" s="13"/>
-      <c r="W16" s="13"/>
-      <c r="X16" s="13"/>
-      <c r="Y16" s="13"/>
-      <c r="Z16" s="13"/>
-      <c r="AA16" s="13"/>
-      <c r="AB16" s="13"/>
-      <c r="AC16" s="13"/>
-      <c r="AD16" s="13"/>
-      <c r="AE16" s="13"/>
-      <c r="AF16" s="13"/>
-      <c r="AG16" s="13"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="7"/>
+      <c r="N16" s="7"/>
+      <c r="O16" s="7"/>
+      <c r="P16" s="7"/>
+      <c r="Q16" s="7"/>
+      <c r="R16" s="7"/>
+      <c r="S16" s="7"/>
+      <c r="T16" s="7"/>
+      <c r="U16" s="7"/>
+      <c r="V16" s="7"/>
+      <c r="W16" s="7"/>
+      <c r="X16" s="7"/>
+      <c r="Y16" s="7"/>
+      <c r="Z16" s="7"/>
+      <c r="AA16" s="7"/>
+      <c r="AB16" s="7"/>
+      <c r="AC16" s="7"/>
+      <c r="AD16" s="7"/>
+      <c r="AE16" s="7"/>
+      <c r="AF16" s="7"/>
+      <c r="AG16" s="7"/>
     </row>
     <row r="17" spans="1:33" ht="22.5" customHeight="1">
-      <c r="A17" s="12"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="10"/>
-      <c r="K17" s="10"/>
-      <c r="L17" s="10"/>
-      <c r="M17" s="10"/>
-      <c r="N17" s="10"/>
-      <c r="O17" s="10"/>
-      <c r="P17" s="10"/>
-      <c r="Q17" s="10"/>
-      <c r="R17" s="10"/>
-      <c r="S17" s="10"/>
-      <c r="T17" s="10"/>
-      <c r="U17" s="10"/>
-      <c r="V17" s="10"/>
-      <c r="W17" s="10"/>
-      <c r="X17" s="10"/>
-      <c r="Y17" s="10"/>
-      <c r="Z17" s="10"/>
-      <c r="AA17" s="10"/>
-      <c r="AB17" s="10"/>
-      <c r="AC17" s="10"/>
-      <c r="AD17" s="10"/>
-      <c r="AE17" s="10"/>
-      <c r="AF17" s="10"/>
-      <c r="AG17" s="10"/>
+      <c r="A17" s="6"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="21"/>
+      <c r="I17" s="21"/>
+      <c r="J17" s="21"/>
+      <c r="K17" s="21"/>
+      <c r="L17" s="21"/>
+      <c r="M17" s="21"/>
+      <c r="N17" s="21"/>
+      <c r="O17" s="21"/>
+      <c r="P17" s="21"/>
+      <c r="Q17" s="21"/>
+      <c r="R17" s="21"/>
+      <c r="S17" s="21"/>
+      <c r="T17" s="21"/>
+      <c r="U17" s="21"/>
+      <c r="V17" s="21"/>
+      <c r="W17" s="21"/>
+      <c r="X17" s="21"/>
+      <c r="Y17" s="21"/>
+      <c r="Z17" s="21"/>
+      <c r="AA17" s="21"/>
+      <c r="AB17" s="21"/>
+      <c r="AC17" s="21"/>
+      <c r="AD17" s="21"/>
+      <c r="AE17" s="21"/>
+      <c r="AF17" s="21"/>
+      <c r="AG17" s="21"/>
     </row>
     <row r="18" spans="1:33" ht="22.5" customHeight="1">
-      <c r="B18" s="8"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="7"/>
-      <c r="M18" s="7"/>
-      <c r="N18" s="7"/>
-      <c r="O18" s="7"/>
-      <c r="P18" s="7"/>
-      <c r="Q18" s="7"/>
-      <c r="R18" s="7"/>
-      <c r="S18" s="7"/>
-      <c r="T18" s="7"/>
-      <c r="U18" s="7"/>
-      <c r="V18" s="7"/>
-      <c r="W18" s="7"/>
-      <c r="X18" s="7"/>
-      <c r="Y18" s="7"/>
-      <c r="Z18" s="7"/>
-      <c r="AA18" s="7"/>
-      <c r="AB18" s="7"/>
-      <c r="AC18" s="7"/>
-      <c r="AD18" s="7"/>
-      <c r="AE18" s="7"/>
-      <c r="AF18" s="7"/>
-      <c r="AG18" s="7"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="22"/>
+      <c r="K18" s="22"/>
+      <c r="L18" s="22"/>
+      <c r="M18" s="22"/>
+      <c r="N18" s="22"/>
+      <c r="O18" s="22"/>
+      <c r="P18" s="22"/>
+      <c r="Q18" s="22"/>
+      <c r="R18" s="22"/>
+      <c r="S18" s="22"/>
+      <c r="T18" s="22"/>
+      <c r="U18" s="22"/>
+      <c r="V18" s="22"/>
+      <c r="W18" s="22"/>
+      <c r="X18" s="22"/>
+      <c r="Y18" s="22"/>
+      <c r="Z18" s="22"/>
+      <c r="AA18" s="22"/>
+      <c r="AB18" s="22"/>
+      <c r="AC18" s="22"/>
+      <c r="AD18" s="22"/>
+      <c r="AE18" s="22"/>
+      <c r="AF18" s="22"/>
+      <c r="AG18" s="22"/>
     </row>
     <row r="19" spans="1:33" ht="22.5" customHeight="1">
-      <c r="B19" s="8"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
-      <c r="K19" s="9"/>
-      <c r="L19" s="9"/>
-      <c r="M19" s="9"/>
-      <c r="N19" s="9"/>
-      <c r="O19" s="9"/>
-      <c r="P19" s="9"/>
-      <c r="Q19" s="9"/>
-      <c r="R19" s="9"/>
-      <c r="S19" s="9"/>
-      <c r="T19" s="9"/>
-      <c r="U19" s="9"/>
-      <c r="V19" s="9"/>
-      <c r="W19" s="9"/>
-      <c r="X19" s="9"/>
-      <c r="Y19" s="9"/>
-      <c r="Z19" s="9"/>
-      <c r="AA19" s="9"/>
-      <c r="AB19" s="9"/>
-      <c r="AC19" s="9"/>
-      <c r="AD19" s="9"/>
-      <c r="AE19" s="9"/>
-      <c r="AF19" s="9"/>
-      <c r="AG19" s="9"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="30"/>
+      <c r="G19" s="30"/>
+      <c r="H19" s="30"/>
+      <c r="I19" s="30"/>
+      <c r="J19" s="30"/>
+      <c r="K19" s="30"/>
+      <c r="L19" s="30"/>
+      <c r="M19" s="30"/>
+      <c r="N19" s="30"/>
+      <c r="O19" s="30"/>
+      <c r="P19" s="30"/>
+      <c r="Q19" s="30"/>
+      <c r="R19" s="30"/>
+      <c r="S19" s="30"/>
+      <c r="T19" s="30"/>
+      <c r="U19" s="30"/>
+      <c r="V19" s="30"/>
+      <c r="W19" s="30"/>
+      <c r="X19" s="30"/>
+      <c r="Y19" s="30"/>
+      <c r="Z19" s="30"/>
+      <c r="AA19" s="30"/>
+      <c r="AB19" s="30"/>
+      <c r="AC19" s="30"/>
+      <c r="AD19" s="30"/>
+      <c r="AE19" s="30"/>
+      <c r="AF19" s="30"/>
+      <c r="AG19" s="30"/>
     </row>
     <row r="20" spans="1:33" ht="22.5" customHeight="1">
-      <c r="B20" s="8"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="7"/>
-      <c r="M20" s="7"/>
-      <c r="N20" s="7"/>
-      <c r="O20" s="7"/>
-      <c r="P20" s="7"/>
-      <c r="Q20" s="7"/>
-      <c r="R20" s="7"/>
-      <c r="S20" s="7"/>
-      <c r="T20" s="7"/>
-      <c r="U20" s="7"/>
-      <c r="V20" s="7"/>
-      <c r="W20" s="7"/>
-      <c r="X20" s="7"/>
-      <c r="Y20" s="7"/>
-      <c r="Z20" s="7"/>
-      <c r="AA20" s="7"/>
-      <c r="AB20" s="7"/>
-      <c r="AC20" s="7"/>
-      <c r="AD20" s="7"/>
-      <c r="AE20" s="7"/>
-      <c r="AF20" s="7"/>
-      <c r="AG20" s="7"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="22"/>
+      <c r="J20" s="22"/>
+      <c r="K20" s="22"/>
+      <c r="L20" s="22"/>
+      <c r="M20" s="22"/>
+      <c r="N20" s="22"/>
+      <c r="O20" s="22"/>
+      <c r="P20" s="22"/>
+      <c r="Q20" s="22"/>
+      <c r="R20" s="22"/>
+      <c r="S20" s="22"/>
+      <c r="T20" s="22"/>
+      <c r="U20" s="22"/>
+      <c r="V20" s="22"/>
+      <c r="W20" s="22"/>
+      <c r="X20" s="22"/>
+      <c r="Y20" s="22"/>
+      <c r="Z20" s="22"/>
+      <c r="AA20" s="22"/>
+      <c r="AB20" s="22"/>
+      <c r="AC20" s="22"/>
+      <c r="AD20" s="22"/>
+      <c r="AE20" s="22"/>
+      <c r="AF20" s="22"/>
+      <c r="AG20" s="22"/>
     </row>
     <row r="21" spans="1:33" ht="19.5" customHeight="1">
-      <c r="B21" s="32" t="s">
+      <c r="B21" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C21" s="33"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="33"/>
-      <c r="F21" s="33"/>
-      <c r="G21" s="33"/>
-      <c r="H21" s="33"/>
-      <c r="I21" s="33"/>
-      <c r="J21" s="33"/>
-      <c r="K21" s="33"/>
-      <c r="L21" s="33"/>
-      <c r="M21" s="33"/>
-      <c r="N21" s="33"/>
-      <c r="O21" s="33"/>
-      <c r="P21" s="33"/>
-      <c r="Q21" s="33"/>
-      <c r="R21" s="33"/>
-      <c r="S21" s="33"/>
-      <c r="T21" s="33"/>
-      <c r="U21" s="33"/>
-      <c r="V21" s="33"/>
-      <c r="W21" s="33"/>
-      <c r="X21" s="33"/>
-      <c r="Y21" s="33"/>
-      <c r="Z21" s="33"/>
-      <c r="AA21" s="33"/>
     </row>
     <row r="22" spans="1:33" ht="198.75" customHeight="1">
-      <c r="B22" s="33"/>
-      <c r="C22" s="33"/>
-      <c r="D22" s="33"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="33"/>
-      <c r="G22" s="33"/>
-      <c r="H22" s="33"/>
-      <c r="I22" s="33"/>
-      <c r="J22" s="33"/>
-      <c r="K22" s="33"/>
-      <c r="L22" s="33"/>
-      <c r="M22" s="33"/>
-      <c r="N22" s="33"/>
-      <c r="O22" s="33"/>
-      <c r="P22" s="33"/>
-      <c r="Q22" s="33"/>
-      <c r="R22" s="33"/>
-      <c r="S22" s="33"/>
-      <c r="T22" s="33"/>
-      <c r="U22" s="33"/>
-      <c r="V22" s="33"/>
-      <c r="W22" s="33"/>
-      <c r="X22" s="33"/>
-      <c r="Y22" s="33"/>
-      <c r="Z22" s="33"/>
-      <c r="AA22" s="33"/>
-      <c r="AB22" s="33"/>
+      <c r="B22" s="34"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="34"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="34"/>
+      <c r="J22" s="34"/>
+      <c r="K22" s="34"/>
+      <c r="L22" s="34"/>
+      <c r="M22" s="34"/>
+      <c r="N22" s="34"/>
+      <c r="O22" s="34"/>
+      <c r="P22" s="34"/>
+      <c r="Q22" s="34"/>
+      <c r="R22" s="34"/>
+      <c r="S22" s="34"/>
+      <c r="T22" s="34"/>
+      <c r="U22" s="34"/>
+      <c r="V22" s="34"/>
+      <c r="W22" s="34"/>
+      <c r="X22" s="34"/>
+      <c r="Y22" s="34"/>
+      <c r="Z22" s="34"/>
+      <c r="AA22" s="34"/>
+      <c r="AB22" s="34"/>
+      <c r="AC22" s="34"/>
+      <c r="AD22" s="34"/>
+      <c r="AE22" s="34"/>
+      <c r="AF22" s="34"/>
+      <c r="AG22" s="34"/>
     </row>
-    <row r="23" spans="1:33" ht="23.25" customHeight="1">
-      <c r="B23" s="33"/>
-      <c r="C23" s="33"/>
-      <c r="D23" s="33"/>
-      <c r="E23" s="33"/>
-      <c r="F23" s="33"/>
-      <c r="G23" s="33"/>
-      <c r="H23" s="33"/>
-      <c r="I23" s="33"/>
-      <c r="J23" s="33"/>
-      <c r="K23" s="33"/>
-      <c r="L23" s="33"/>
-      <c r="M23" s="33"/>
-      <c r="N23" s="33"/>
-      <c r="O23" s="33"/>
-      <c r="P23" s="33"/>
-      <c r="Q23" s="33"/>
-      <c r="R23" s="33"/>
-      <c r="S23" s="33"/>
-      <c r="T23" s="33"/>
-      <c r="U23" s="33"/>
-      <c r="V23" s="33"/>
-      <c r="W23" s="33"/>
-      <c r="X23" s="33"/>
-      <c r="Y23" s="33"/>
-      <c r="Z23" s="33"/>
-      <c r="AA23" s="33"/>
-      <c r="AB23" s="33"/>
-    </row>
+    <row r="23" spans="1:33" ht="23.25" customHeight="1"/>
     <row r="24" spans="1:33" ht="23.25" customHeight="1">
-      <c r="B24" s="33"/>
-      <c r="C24" s="33"/>
-      <c r="D24" s="33"/>
-      <c r="E24" s="33"/>
-      <c r="F24" s="33"/>
-      <c r="G24" s="33"/>
-      <c r="H24" s="33"/>
-      <c r="I24" s="33"/>
-      <c r="J24" s="33"/>
-      <c r="K24" s="33"/>
-      <c r="L24" s="33"/>
-      <c r="M24" s="33"/>
-      <c r="N24" s="33"/>
-      <c r="O24" s="33"/>
-      <c r="P24" s="33"/>
-      <c r="Q24" s="33"/>
-      <c r="R24" s="33"/>
-      <c r="S24" s="33"/>
-      <c r="T24" s="33"/>
-      <c r="U24" s="33"/>
-      <c r="V24" s="33"/>
-      <c r="W24" s="33"/>
-      <c r="X24" s="33"/>
-      <c r="Y24" s="33"/>
-      <c r="Z24" s="33"/>
-      <c r="AA24" s="33"/>
-      <c r="AB24" s="6"/>
-      <c r="AC24" s="5"/>
-      <c r="AD24" s="5"/>
-      <c r="AE24" s="5"/>
-      <c r="AF24" s="5"/>
-      <c r="AG24" s="5"/>
+      <c r="AB24" s="3"/>
+      <c r="AC24" s="33"/>
+      <c r="AD24" s="33"/>
+      <c r="AE24" s="33"/>
+      <c r="AF24" s="33"/>
+      <c r="AG24" s="33"/>
     </row>
     <row r="25" spans="1:33" ht="23.25" customHeight="1">
-      <c r="AC25" s="4" t="s">
+      <c r="AC25" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="AD25" s="4"/>
-      <c r="AE25" s="4"/>
-      <c r="AF25" s="4"/>
-      <c r="AG25" s="4"/>
+      <c r="AD25" s="31"/>
+      <c r="AE25" s="31"/>
+      <c r="AF25" s="31"/>
+      <c r="AG25" s="31"/>
     </row>
     <row r="26" spans="1:33" ht="10.5" customHeight="1"/>
     <row r="27" spans="1:33" ht="14.25" customHeight="1">
-      <c r="C27" s="3"/>
-      <c r="AC27" s="2" t="s">
+      <c r="C27" s="2"/>
+      <c r="AC27" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="AD27" s="2"/>
-      <c r="AE27" s="2"/>
-      <c r="AF27" s="2"/>
-      <c r="AG27" s="2"/>
+      <c r="AD27" s="32"/>
+      <c r="AE27" s="32"/>
+      <c r="AF27" s="32"/>
+      <c r="AG27" s="32"/>
     </row>
   </sheetData>
-  <mergeCells count="71">
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="F17:F18"/>
-    <mergeCell ref="S17:S18"/>
-    <mergeCell ref="H17:H18"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="J17:J18"/>
-    <mergeCell ref="A1:AA2"/>
-    <mergeCell ref="AB1:AG1"/>
-    <mergeCell ref="AB2:AG2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:AG4"/>
-    <mergeCell ref="K17:K18"/>
-    <mergeCell ref="L17:L18"/>
-    <mergeCell ref="M17:M18"/>
-    <mergeCell ref="N17:N18"/>
-    <mergeCell ref="O17:O18"/>
-    <mergeCell ref="G17:G18"/>
-    <mergeCell ref="AE17:AE18"/>
-    <mergeCell ref="T17:T18"/>
-    <mergeCell ref="U17:U18"/>
-    <mergeCell ref="V17:V18"/>
-    <mergeCell ref="W17:W18"/>
-    <mergeCell ref="X17:X18"/>
-    <mergeCell ref="Y17:Y18"/>
-    <mergeCell ref="Z17:Z18"/>
-    <mergeCell ref="AA17:AA18"/>
-    <mergeCell ref="AB17:AB18"/>
-    <mergeCell ref="AC17:AC18"/>
-    <mergeCell ref="AD17:AD18"/>
-    <mergeCell ref="P17:P18"/>
-    <mergeCell ref="Q17:Q18"/>
+  <mergeCells count="72">
+    <mergeCell ref="AC25:AG25"/>
+    <mergeCell ref="AC27:AG27"/>
+    <mergeCell ref="AC19:AC20"/>
+    <mergeCell ref="AD19:AD20"/>
+    <mergeCell ref="AE19:AE20"/>
+    <mergeCell ref="AF19:AF20"/>
+    <mergeCell ref="AG19:AG20"/>
+    <mergeCell ref="AC24:AG24"/>
+    <mergeCell ref="B22:AG22"/>
+    <mergeCell ref="N19:N20"/>
+    <mergeCell ref="O19:O20"/>
+    <mergeCell ref="P19:P20"/>
+    <mergeCell ref="AB19:AB20"/>
+    <mergeCell ref="Q19:Q20"/>
+    <mergeCell ref="R19:R20"/>
+    <mergeCell ref="S19:S20"/>
+    <mergeCell ref="T19:T20"/>
+    <mergeCell ref="U19:U20"/>
+    <mergeCell ref="V19:V20"/>
+    <mergeCell ref="W19:W20"/>
+    <mergeCell ref="X19:X20"/>
+    <mergeCell ref="Y19:Y20"/>
     <mergeCell ref="R17:R18"/>
     <mergeCell ref="AF17:AF18"/>
     <mergeCell ref="AG17:AG18"/>
@@ -2458,27 +2374,40 @@
     <mergeCell ref="K19:K20"/>
     <mergeCell ref="L19:L20"/>
     <mergeCell ref="M19:M20"/>
-    <mergeCell ref="N19:N20"/>
-    <mergeCell ref="O19:O20"/>
-    <mergeCell ref="P19:P20"/>
-    <mergeCell ref="AB19:AB20"/>
-    <mergeCell ref="Q19:Q20"/>
-    <mergeCell ref="R19:R20"/>
-    <mergeCell ref="S19:S20"/>
-    <mergeCell ref="T19:T20"/>
-    <mergeCell ref="U19:U20"/>
-    <mergeCell ref="V19:V20"/>
-    <mergeCell ref="W19:W20"/>
-    <mergeCell ref="X19:X20"/>
-    <mergeCell ref="Y19:Y20"/>
-    <mergeCell ref="AC25:AG25"/>
-    <mergeCell ref="AC27:AG27"/>
-    <mergeCell ref="AC19:AC20"/>
-    <mergeCell ref="AD19:AD20"/>
-    <mergeCell ref="AE19:AE20"/>
-    <mergeCell ref="AF19:AF20"/>
-    <mergeCell ref="AG19:AG20"/>
-    <mergeCell ref="AC24:AG24"/>
+    <mergeCell ref="AE17:AE18"/>
+    <mergeCell ref="T17:T18"/>
+    <mergeCell ref="U17:U18"/>
+    <mergeCell ref="V17:V18"/>
+    <mergeCell ref="W17:W18"/>
+    <mergeCell ref="X17:X18"/>
+    <mergeCell ref="Y17:Y18"/>
+    <mergeCell ref="Z17:Z18"/>
+    <mergeCell ref="AA17:AA18"/>
+    <mergeCell ref="AB17:AB18"/>
+    <mergeCell ref="AC17:AC18"/>
+    <mergeCell ref="AD17:AD18"/>
+    <mergeCell ref="A1:AA2"/>
+    <mergeCell ref="AB1:AG1"/>
+    <mergeCell ref="AB2:AG2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:AG4"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="S17:S18"/>
+    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="J17:J18"/>
+    <mergeCell ref="K17:K18"/>
+    <mergeCell ref="L17:L18"/>
+    <mergeCell ref="M17:M18"/>
+    <mergeCell ref="N17:N18"/>
+    <mergeCell ref="O17:O18"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="P17:P18"/>
+    <mergeCell ref="Q17:Q18"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>

--- a/FM-MN-07_LATHE-01.xlsx
+++ b/FM-MN-07_LATHE-01.xlsx
@@ -289,7 +289,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
@@ -393,6 +393,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1703,37 +1706,37 @@
           <t>การ WORM SPINDLE ก่อนเริ่มงาน 15 นาที</t>
         </is>
       </c>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
-      <c r="E6" s="7" t="n"/>
-      <c r="F6" s="7" t="n"/>
-      <c r="G6" s="7" t="n"/>
-      <c r="H6" s="7" t="n"/>
-      <c r="I6" s="7" t="n"/>
-      <c r="J6" s="7" t="n"/>
-      <c r="K6" s="7" t="n"/>
-      <c r="L6" s="7" t="n"/>
-      <c r="M6" s="7" t="n"/>
-      <c r="N6" s="7" t="n"/>
-      <c r="O6" s="7" t="n"/>
-      <c r="P6" s="7" t="n"/>
-      <c r="Q6" s="7" t="n"/>
-      <c r="R6" s="7" t="n"/>
-      <c r="S6" s="7" t="n"/>
-      <c r="T6" s="7" t="n"/>
-      <c r="U6" s="7" t="n"/>
-      <c r="V6" s="7" t="n"/>
-      <c r="W6" s="7" t="n"/>
-      <c r="X6" s="7" t="n"/>
-      <c r="Y6" s="7" t="n"/>
-      <c r="Z6" s="7" t="n"/>
-      <c r="AA6" s="7" t="n"/>
-      <c r="AB6" s="7" t="n"/>
-      <c r="AC6" s="7" t="n"/>
-      <c r="AD6" s="7" t="n"/>
-      <c r="AE6" s="7" t="n"/>
-      <c r="AF6" s="7" t="n"/>
-      <c r="AG6" s="7" t="n"/>
+      <c r="C6" s="7" t="inlineStr"/>
+      <c r="D6" s="7" t="inlineStr"/>
+      <c r="E6" s="7" t="inlineStr"/>
+      <c r="F6" s="7" t="inlineStr"/>
+      <c r="G6" s="7" t="inlineStr"/>
+      <c r="H6" s="7" t="inlineStr"/>
+      <c r="I6" s="7" t="inlineStr"/>
+      <c r="J6" s="7" t="inlineStr"/>
+      <c r="K6" s="7" t="inlineStr"/>
+      <c r="L6" s="7" t="inlineStr"/>
+      <c r="M6" s="7" t="inlineStr"/>
+      <c r="N6" s="7" t="inlineStr"/>
+      <c r="O6" s="7" t="inlineStr"/>
+      <c r="P6" s="7" t="inlineStr"/>
+      <c r="Q6" s="7" t="inlineStr"/>
+      <c r="R6" s="7" t="inlineStr"/>
+      <c r="S6" s="7" t="inlineStr"/>
+      <c r="T6" s="7" t="inlineStr"/>
+      <c r="U6" s="7" t="inlineStr"/>
+      <c r="V6" s="7" t="inlineStr"/>
+      <c r="W6" s="7" t="inlineStr"/>
+      <c r="X6" s="7" t="inlineStr"/>
+      <c r="Y6" s="7" t="inlineStr"/>
+      <c r="Z6" s="7" t="inlineStr"/>
+      <c r="AA6" s="7" t="inlineStr"/>
+      <c r="AB6" s="7" t="inlineStr"/>
+      <c r="AC6" s="7" t="inlineStr"/>
+      <c r="AD6" s="7" t="inlineStr"/>
+      <c r="AE6" s="7" t="inlineStr"/>
+      <c r="AF6" s="7" t="inlineStr"/>
+      <c r="AG6" s="7" t="inlineStr"/>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="9" t="n">
@@ -1744,37 +1747,37 @@
           <t>เช็คระดับน้ำมันเครื่องในห้องเกียร์</t>
         </is>
       </c>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="7" t="n"/>
-      <c r="F7" s="7" t="n"/>
-      <c r="G7" s="7" t="n"/>
-      <c r="H7" s="7" t="n"/>
-      <c r="I7" s="7" t="n"/>
-      <c r="J7" s="7" t="n"/>
-      <c r="K7" s="7" t="n"/>
-      <c r="L7" s="7" t="n"/>
-      <c r="M7" s="7" t="n"/>
-      <c r="N7" s="7" t="n"/>
-      <c r="O7" s="7" t="n"/>
-      <c r="P7" s="7" t="n"/>
-      <c r="Q7" s="7" t="n"/>
-      <c r="R7" s="7" t="n"/>
-      <c r="S7" s="7" t="n"/>
-      <c r="T7" s="7" t="n"/>
-      <c r="U7" s="7" t="n"/>
-      <c r="V7" s="7" t="n"/>
-      <c r="W7" s="7" t="n"/>
-      <c r="X7" s="7" t="n"/>
-      <c r="Y7" s="7" t="n"/>
-      <c r="Z7" s="7" t="n"/>
-      <c r="AA7" s="7" t="n"/>
-      <c r="AB7" s="7" t="n"/>
-      <c r="AC7" s="7" t="n"/>
-      <c r="AD7" s="7" t="n"/>
-      <c r="AE7" s="7" t="n"/>
-      <c r="AF7" s="7" t="n"/>
-      <c r="AG7" s="7" t="n"/>
+      <c r="C7" s="7" t="inlineStr"/>
+      <c r="D7" s="7" t="inlineStr"/>
+      <c r="E7" s="7" t="inlineStr"/>
+      <c r="F7" s="7" t="inlineStr"/>
+      <c r="G7" s="7" t="inlineStr"/>
+      <c r="H7" s="7" t="inlineStr"/>
+      <c r="I7" s="7" t="inlineStr"/>
+      <c r="J7" s="7" t="inlineStr"/>
+      <c r="K7" s="7" t="inlineStr"/>
+      <c r="L7" s="7" t="inlineStr"/>
+      <c r="M7" s="7" t="inlineStr"/>
+      <c r="N7" s="7" t="inlineStr"/>
+      <c r="O7" s="7" t="inlineStr"/>
+      <c r="P7" s="7" t="inlineStr"/>
+      <c r="Q7" s="7" t="inlineStr"/>
+      <c r="R7" s="7" t="inlineStr"/>
+      <c r="S7" s="7" t="inlineStr"/>
+      <c r="T7" s="7" t="inlineStr"/>
+      <c r="U7" s="7" t="inlineStr"/>
+      <c r="V7" s="7" t="inlineStr"/>
+      <c r="W7" s="7" t="inlineStr"/>
+      <c r="X7" s="7" t="inlineStr"/>
+      <c r="Y7" s="7" t="inlineStr"/>
+      <c r="Z7" s="7" t="inlineStr"/>
+      <c r="AA7" s="7" t="inlineStr"/>
+      <c r="AB7" s="7" t="inlineStr"/>
+      <c r="AC7" s="7" t="inlineStr"/>
+      <c r="AD7" s="7" t="inlineStr"/>
+      <c r="AE7" s="7" t="inlineStr"/>
+      <c r="AF7" s="7" t="inlineStr"/>
+      <c r="AG7" s="7" t="inlineStr"/>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="9" t="n">
@@ -1785,37 +1788,37 @@
           <t>เช็คระบบเฟื่องทดลองเปลี่ยนรอบตวามเร็วต่าง ๆ</t>
         </is>
       </c>
-      <c r="C8" s="7" t="n"/>
-      <c r="D8" s="7" t="n"/>
-      <c r="E8" s="7" t="n"/>
-      <c r="F8" s="7" t="n"/>
-      <c r="G8" s="7" t="n"/>
-      <c r="H8" s="7" t="n"/>
-      <c r="I8" s="7" t="n"/>
-      <c r="J8" s="7" t="n"/>
-      <c r="K8" s="7" t="n"/>
-      <c r="L8" s="7" t="n"/>
-      <c r="M8" s="7" t="n"/>
-      <c r="N8" s="7" t="n"/>
-      <c r="O8" s="7" t="n"/>
-      <c r="P8" s="7" t="n"/>
-      <c r="Q8" s="7" t="n"/>
-      <c r="R8" s="7" t="n"/>
-      <c r="S8" s="7" t="n"/>
-      <c r="T8" s="7" t="n"/>
-      <c r="U8" s="7" t="n"/>
-      <c r="V8" s="7" t="n"/>
-      <c r="W8" s="7" t="n"/>
-      <c r="X8" s="7" t="n"/>
-      <c r="Y8" s="7" t="n"/>
-      <c r="Z8" s="7" t="n"/>
-      <c r="AA8" s="7" t="n"/>
-      <c r="AB8" s="7" t="n"/>
-      <c r="AC8" s="7" t="n"/>
-      <c r="AD8" s="7" t="n"/>
-      <c r="AE8" s="7" t="n"/>
-      <c r="AF8" s="7" t="n"/>
-      <c r="AG8" s="7" t="n"/>
+      <c r="C8" s="7" t="inlineStr"/>
+      <c r="D8" s="7" t="inlineStr"/>
+      <c r="E8" s="7" t="inlineStr"/>
+      <c r="F8" s="7" t="inlineStr"/>
+      <c r="G8" s="7" t="inlineStr"/>
+      <c r="H8" s="7" t="inlineStr"/>
+      <c r="I8" s="7" t="inlineStr"/>
+      <c r="J8" s="7" t="inlineStr"/>
+      <c r="K8" s="7" t="inlineStr"/>
+      <c r="L8" s="7" t="inlineStr"/>
+      <c r="M8" s="7" t="inlineStr"/>
+      <c r="N8" s="7" t="inlineStr"/>
+      <c r="O8" s="7" t="inlineStr"/>
+      <c r="P8" s="7" t="inlineStr"/>
+      <c r="Q8" s="7" t="inlineStr"/>
+      <c r="R8" s="7" t="inlineStr"/>
+      <c r="S8" s="7" t="inlineStr"/>
+      <c r="T8" s="7" t="inlineStr"/>
+      <c r="U8" s="7" t="inlineStr"/>
+      <c r="V8" s="7" t="inlineStr"/>
+      <c r="W8" s="7" t="inlineStr"/>
+      <c r="X8" s="7" t="inlineStr"/>
+      <c r="Y8" s="7" t="inlineStr"/>
+      <c r="Z8" s="7" t="inlineStr"/>
+      <c r="AA8" s="7" t="inlineStr"/>
+      <c r="AB8" s="7" t="inlineStr"/>
+      <c r="AC8" s="7" t="inlineStr"/>
+      <c r="AD8" s="7" t="inlineStr"/>
+      <c r="AE8" s="7" t="inlineStr"/>
+      <c r="AF8" s="7" t="inlineStr"/>
+      <c r="AG8" s="7" t="inlineStr"/>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="9" t="n">
@@ -1826,37 +1829,37 @@
           <t>เช็ค AUTO แกน X,Y</t>
         </is>
       </c>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="7" t="n"/>
-      <c r="G9" s="7" t="n"/>
-      <c r="H9" s="7" t="n"/>
-      <c r="I9" s="7" t="n"/>
-      <c r="J9" s="7" t="n"/>
-      <c r="K9" s="7" t="n"/>
-      <c r="L9" s="7" t="n"/>
-      <c r="M9" s="7" t="n"/>
-      <c r="N9" s="7" t="n"/>
-      <c r="O9" s="7" t="n"/>
-      <c r="P9" s="7" t="n"/>
-      <c r="Q9" s="7" t="n"/>
-      <c r="R9" s="7" t="n"/>
-      <c r="S9" s="7" t="n"/>
-      <c r="T9" s="7" t="n"/>
-      <c r="U9" s="7" t="n"/>
-      <c r="V9" s="7" t="n"/>
-      <c r="W9" s="7" t="n"/>
-      <c r="X9" s="7" t="n"/>
-      <c r="Y9" s="7" t="n"/>
-      <c r="Z9" s="7" t="n"/>
-      <c r="AA9" s="7" t="n"/>
-      <c r="AB9" s="7" t="n"/>
-      <c r="AC9" s="7" t="n"/>
-      <c r="AD9" s="7" t="n"/>
-      <c r="AE9" s="7" t="n"/>
-      <c r="AF9" s="7" t="n"/>
-      <c r="AG9" s="7" t="n"/>
+      <c r="C9" s="7" t="inlineStr"/>
+      <c r="D9" s="7" t="inlineStr"/>
+      <c r="E9" s="7" t="inlineStr"/>
+      <c r="F9" s="7" t="inlineStr"/>
+      <c r="G9" s="7" t="inlineStr"/>
+      <c r="H9" s="7" t="inlineStr"/>
+      <c r="I9" s="7" t="inlineStr"/>
+      <c r="J9" s="7" t="inlineStr"/>
+      <c r="K9" s="7" t="inlineStr"/>
+      <c r="L9" s="7" t="inlineStr"/>
+      <c r="M9" s="7" t="inlineStr"/>
+      <c r="N9" s="7" t="inlineStr"/>
+      <c r="O9" s="7" t="inlineStr"/>
+      <c r="P9" s="7" t="inlineStr"/>
+      <c r="Q9" s="7" t="inlineStr"/>
+      <c r="R9" s="7" t="inlineStr"/>
+      <c r="S9" s="7" t="inlineStr"/>
+      <c r="T9" s="7" t="inlineStr"/>
+      <c r="U9" s="7" t="inlineStr"/>
+      <c r="V9" s="7" t="inlineStr"/>
+      <c r="W9" s="7" t="inlineStr"/>
+      <c r="X9" s="7" t="inlineStr"/>
+      <c r="Y9" s="7" t="inlineStr"/>
+      <c r="Z9" s="7" t="inlineStr"/>
+      <c r="AA9" s="7" t="inlineStr"/>
+      <c r="AB9" s="7" t="inlineStr"/>
+      <c r="AC9" s="7" t="inlineStr"/>
+      <c r="AD9" s="7" t="inlineStr"/>
+      <c r="AE9" s="7" t="inlineStr"/>
+      <c r="AF9" s="7" t="inlineStr"/>
+      <c r="AG9" s="7" t="inlineStr"/>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="9" t="n">
@@ -1867,37 +1870,37 @@
           <t>เช็คระดับน้ำมันหล่อลื่นใน PUMP</t>
         </is>
       </c>
-      <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n"/>
-      <c r="E10" s="7" t="n"/>
-      <c r="F10" s="7" t="n"/>
-      <c r="G10" s="7" t="n"/>
-      <c r="H10" s="7" t="n"/>
-      <c r="I10" s="7" t="n"/>
-      <c r="J10" s="7" t="n"/>
-      <c r="K10" s="7" t="n"/>
-      <c r="L10" s="7" t="n"/>
-      <c r="M10" s="7" t="n"/>
-      <c r="N10" s="7" t="n"/>
-      <c r="O10" s="7" t="n"/>
-      <c r="P10" s="7" t="n"/>
-      <c r="Q10" s="7" t="n"/>
-      <c r="R10" s="7" t="n"/>
-      <c r="S10" s="7" t="n"/>
-      <c r="T10" s="7" t="n"/>
-      <c r="U10" s="7" t="n"/>
-      <c r="V10" s="7" t="n"/>
-      <c r="W10" s="7" t="n"/>
-      <c r="X10" s="7" t="n"/>
-      <c r="Y10" s="7" t="n"/>
-      <c r="Z10" s="7" t="n"/>
-      <c r="AA10" s="7" t="n"/>
-      <c r="AB10" s="7" t="n"/>
-      <c r="AC10" s="7" t="n"/>
-      <c r="AD10" s="7" t="n"/>
-      <c r="AE10" s="7" t="n"/>
-      <c r="AF10" s="7" t="n"/>
-      <c r="AG10" s="7" t="n"/>
+      <c r="C10" s="7" t="inlineStr"/>
+      <c r="D10" s="7" t="inlineStr"/>
+      <c r="E10" s="7" t="inlineStr"/>
+      <c r="F10" s="7" t="inlineStr"/>
+      <c r="G10" s="7" t="inlineStr"/>
+      <c r="H10" s="7" t="inlineStr"/>
+      <c r="I10" s="7" t="inlineStr"/>
+      <c r="J10" s="7" t="inlineStr"/>
+      <c r="K10" s="7" t="inlineStr"/>
+      <c r="L10" s="7" t="inlineStr"/>
+      <c r="M10" s="7" t="inlineStr"/>
+      <c r="N10" s="7" t="inlineStr"/>
+      <c r="O10" s="7" t="inlineStr"/>
+      <c r="P10" s="7" t="inlineStr"/>
+      <c r="Q10" s="7" t="inlineStr"/>
+      <c r="R10" s="7" t="inlineStr"/>
+      <c r="S10" s="7" t="inlineStr"/>
+      <c r="T10" s="7" t="inlineStr"/>
+      <c r="U10" s="7" t="inlineStr"/>
+      <c r="V10" s="7" t="inlineStr"/>
+      <c r="W10" s="7" t="inlineStr"/>
+      <c r="X10" s="7" t="inlineStr"/>
+      <c r="Y10" s="7" t="inlineStr"/>
+      <c r="Z10" s="7" t="inlineStr"/>
+      <c r="AA10" s="7" t="inlineStr"/>
+      <c r="AB10" s="7" t="inlineStr"/>
+      <c r="AC10" s="7" t="inlineStr"/>
+      <c r="AD10" s="7" t="inlineStr"/>
+      <c r="AE10" s="7" t="inlineStr"/>
+      <c r="AF10" s="7" t="inlineStr"/>
+      <c r="AG10" s="7" t="inlineStr"/>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="9" t="n">
@@ -1908,37 +1911,37 @@
           <t>เช็คน้ำมันหล่อเย็นและการทำงานของปั้ม</t>
         </is>
       </c>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="7" t="n"/>
-      <c r="G11" s="7" t="n"/>
-      <c r="H11" s="7" t="n"/>
-      <c r="I11" s="7" t="n"/>
-      <c r="J11" s="7" t="n"/>
-      <c r="K11" s="7" t="n"/>
-      <c r="L11" s="7" t="n"/>
-      <c r="M11" s="7" t="n"/>
-      <c r="N11" s="7" t="n"/>
-      <c r="O11" s="7" t="n"/>
-      <c r="P11" s="7" t="n"/>
-      <c r="Q11" s="7" t="n"/>
-      <c r="R11" s="7" t="n"/>
-      <c r="S11" s="7" t="n"/>
-      <c r="T11" s="7" t="n"/>
-      <c r="U11" s="7" t="n"/>
-      <c r="V11" s="7" t="n"/>
-      <c r="W11" s="7" t="n"/>
-      <c r="X11" s="7" t="n"/>
-      <c r="Y11" s="7" t="n"/>
-      <c r="Z11" s="7" t="n"/>
-      <c r="AA11" s="7" t="n"/>
-      <c r="AB11" s="7" t="n"/>
-      <c r="AC11" s="7" t="n"/>
-      <c r="AD11" s="7" t="n"/>
-      <c r="AE11" s="7" t="n"/>
-      <c r="AF11" s="7" t="n"/>
-      <c r="AG11" s="7" t="n"/>
+      <c r="C11" s="7" t="inlineStr"/>
+      <c r="D11" s="7" t="inlineStr"/>
+      <c r="E11" s="7" t="inlineStr"/>
+      <c r="F11" s="7" t="inlineStr"/>
+      <c r="G11" s="7" t="inlineStr"/>
+      <c r="H11" s="7" t="inlineStr"/>
+      <c r="I11" s="7" t="inlineStr"/>
+      <c r="J11" s="7" t="inlineStr"/>
+      <c r="K11" s="7" t="inlineStr"/>
+      <c r="L11" s="7" t="inlineStr"/>
+      <c r="M11" s="7" t="inlineStr"/>
+      <c r="N11" s="7" t="inlineStr"/>
+      <c r="O11" s="7" t="inlineStr"/>
+      <c r="P11" s="7" t="inlineStr"/>
+      <c r="Q11" s="7" t="inlineStr"/>
+      <c r="R11" s="7" t="inlineStr"/>
+      <c r="S11" s="7" t="inlineStr"/>
+      <c r="T11" s="7" t="inlineStr"/>
+      <c r="U11" s="7" t="inlineStr"/>
+      <c r="V11" s="7" t="inlineStr"/>
+      <c r="W11" s="7" t="inlineStr"/>
+      <c r="X11" s="7" t="inlineStr"/>
+      <c r="Y11" s="7" t="inlineStr"/>
+      <c r="Z11" s="7" t="inlineStr"/>
+      <c r="AA11" s="7" t="inlineStr"/>
+      <c r="AB11" s="7" t="inlineStr"/>
+      <c r="AC11" s="7" t="inlineStr"/>
+      <c r="AD11" s="7" t="inlineStr"/>
+      <c r="AE11" s="7" t="inlineStr"/>
+      <c r="AF11" s="7" t="inlineStr"/>
+      <c r="AG11" s="7" t="inlineStr"/>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="20" t="n">
@@ -1949,37 +1952,37 @@
           <t>ตรวจสอบหน้าจอ  DIGITAL  READ OUT และการ ทำงานของ  LINEAR  SCALE</t>
         </is>
       </c>
-      <c r="C12" s="11" t="n"/>
-      <c r="D12" s="11" t="n"/>
-      <c r="E12" s="11" t="n"/>
-      <c r="F12" s="11" t="n"/>
-      <c r="G12" s="11" t="n"/>
-      <c r="H12" s="11" t="n"/>
-      <c r="I12" s="11" t="n"/>
-      <c r="J12" s="11" t="n"/>
-      <c r="K12" s="11" t="n"/>
-      <c r="L12" s="11" t="n"/>
-      <c r="M12" s="11" t="n"/>
-      <c r="N12" s="11" t="n"/>
-      <c r="O12" s="11" t="n"/>
-      <c r="P12" s="11" t="n"/>
-      <c r="Q12" s="11" t="n"/>
-      <c r="R12" s="11" t="n"/>
-      <c r="S12" s="11" t="n"/>
-      <c r="T12" s="11" t="n"/>
-      <c r="U12" s="11" t="n"/>
-      <c r="V12" s="11" t="n"/>
-      <c r="W12" s="11" t="n"/>
-      <c r="X12" s="11" t="n"/>
-      <c r="Y12" s="11" t="n"/>
-      <c r="Z12" s="11" t="n"/>
-      <c r="AA12" s="11" t="n"/>
-      <c r="AB12" s="11" t="n"/>
-      <c r="AC12" s="11" t="n"/>
-      <c r="AD12" s="11" t="n"/>
-      <c r="AE12" s="11" t="n"/>
-      <c r="AF12" s="11" t="n"/>
-      <c r="AG12" s="11" t="n"/>
+      <c r="C12" s="11" t="inlineStr"/>
+      <c r="D12" s="11" t="inlineStr"/>
+      <c r="E12" s="11" t="inlineStr"/>
+      <c r="F12" s="11" t="inlineStr"/>
+      <c r="G12" s="11" t="inlineStr"/>
+      <c r="H12" s="11" t="inlineStr"/>
+      <c r="I12" s="11" t="inlineStr"/>
+      <c r="J12" s="11" t="inlineStr"/>
+      <c r="K12" s="11" t="inlineStr"/>
+      <c r="L12" s="11" t="inlineStr"/>
+      <c r="M12" s="11" t="inlineStr"/>
+      <c r="N12" s="11" t="inlineStr"/>
+      <c r="O12" s="11" t="inlineStr"/>
+      <c r="P12" s="11" t="inlineStr"/>
+      <c r="Q12" s="11" t="inlineStr"/>
+      <c r="R12" s="11" t="inlineStr"/>
+      <c r="S12" s="11" t="inlineStr"/>
+      <c r="T12" s="11" t="inlineStr"/>
+      <c r="U12" s="11" t="inlineStr"/>
+      <c r="V12" s="11" t="inlineStr"/>
+      <c r="W12" s="11" t="inlineStr"/>
+      <c r="X12" s="11" t="inlineStr"/>
+      <c r="Y12" s="11" t="inlineStr"/>
+      <c r="Z12" s="11" t="inlineStr"/>
+      <c r="AA12" s="11" t="inlineStr"/>
+      <c r="AB12" s="11" t="inlineStr"/>
+      <c r="AC12" s="11" t="inlineStr"/>
+      <c r="AD12" s="11" t="inlineStr"/>
+      <c r="AE12" s="11" t="inlineStr"/>
+      <c r="AF12" s="11" t="inlineStr"/>
+      <c r="AG12" s="11" t="inlineStr"/>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="9" t="n">
@@ -1990,37 +1993,37 @@
           <t>ตรวจเช็คสภาพและความตึงของสายพาน</t>
         </is>
       </c>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="n"/>
-      <c r="E13" s="7" t="n"/>
-      <c r="F13" s="7" t="n"/>
-      <c r="G13" s="7" t="n"/>
-      <c r="H13" s="7" t="n"/>
-      <c r="I13" s="7" t="n"/>
-      <c r="J13" s="7" t="n"/>
-      <c r="K13" s="7" t="n"/>
-      <c r="L13" s="7" t="n"/>
-      <c r="M13" s="7" t="n"/>
-      <c r="N13" s="7" t="n"/>
-      <c r="O13" s="7" t="n"/>
-      <c r="P13" s="7" t="n"/>
-      <c r="Q13" s="7" t="n"/>
-      <c r="R13" s="7" t="n"/>
-      <c r="S13" s="7" t="n"/>
-      <c r="T13" s="7" t="n"/>
-      <c r="U13" s="7" t="n"/>
-      <c r="V13" s="7" t="n"/>
-      <c r="W13" s="7" t="n"/>
-      <c r="X13" s="7" t="n"/>
-      <c r="Y13" s="7" t="n"/>
-      <c r="Z13" s="7" t="n"/>
-      <c r="AA13" s="7" t="n"/>
-      <c r="AB13" s="7" t="n"/>
-      <c r="AC13" s="7" t="n"/>
-      <c r="AD13" s="7" t="n"/>
-      <c r="AE13" s="7" t="n"/>
-      <c r="AF13" s="7" t="n"/>
-      <c r="AG13" s="7" t="n"/>
+      <c r="C13" s="7" t="inlineStr"/>
+      <c r="D13" s="7" t="inlineStr"/>
+      <c r="E13" s="7" t="inlineStr"/>
+      <c r="F13" s="7" t="inlineStr"/>
+      <c r="G13" s="7" t="inlineStr"/>
+      <c r="H13" s="7" t="inlineStr"/>
+      <c r="I13" s="7" t="inlineStr"/>
+      <c r="J13" s="7" t="inlineStr"/>
+      <c r="K13" s="7" t="inlineStr"/>
+      <c r="L13" s="7" t="inlineStr"/>
+      <c r="M13" s="7" t="inlineStr"/>
+      <c r="N13" s="7" t="inlineStr"/>
+      <c r="O13" s="7" t="inlineStr"/>
+      <c r="P13" s="7" t="inlineStr"/>
+      <c r="Q13" s="7" t="inlineStr"/>
+      <c r="R13" s="7" t="inlineStr"/>
+      <c r="S13" s="7" t="inlineStr"/>
+      <c r="T13" s="7" t="inlineStr"/>
+      <c r="U13" s="7" t="inlineStr"/>
+      <c r="V13" s="7" t="inlineStr"/>
+      <c r="W13" s="7" t="inlineStr"/>
+      <c r="X13" s="7" t="inlineStr"/>
+      <c r="Y13" s="7" t="inlineStr"/>
+      <c r="Z13" s="7" t="inlineStr"/>
+      <c r="AA13" s="7" t="inlineStr"/>
+      <c r="AB13" s="7" t="inlineStr"/>
+      <c r="AC13" s="7" t="inlineStr"/>
+      <c r="AD13" s="7" t="inlineStr"/>
+      <c r="AE13" s="7" t="inlineStr"/>
+      <c r="AF13" s="7" t="inlineStr"/>
+      <c r="AG13" s="7" t="inlineStr"/>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="9" t="n">
@@ -2031,37 +2034,37 @@
           <t>ตรวจสอบการทำงานของไฟฟ้าแสงสว่าง</t>
         </is>
       </c>
-      <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="n"/>
-      <c r="E14" s="7" t="n"/>
-      <c r="F14" s="7" t="n"/>
-      <c r="G14" s="7" t="n"/>
-      <c r="H14" s="7" t="n"/>
-      <c r="I14" s="7" t="n"/>
-      <c r="J14" s="7" t="n"/>
-      <c r="K14" s="7" t="n"/>
-      <c r="L14" s="7" t="n"/>
-      <c r="M14" s="7" t="n"/>
-      <c r="N14" s="7" t="n"/>
-      <c r="O14" s="7" t="n"/>
-      <c r="P14" s="7" t="n"/>
-      <c r="Q14" s="7" t="n"/>
-      <c r="R14" s="7" t="n"/>
-      <c r="S14" s="7" t="n"/>
-      <c r="T14" s="7" t="n"/>
-      <c r="U14" s="7" t="n"/>
-      <c r="V14" s="7" t="n"/>
-      <c r="W14" s="7" t="n"/>
-      <c r="X14" s="7" t="n"/>
-      <c r="Y14" s="7" t="n"/>
-      <c r="Z14" s="7" t="n"/>
-      <c r="AA14" s="7" t="n"/>
-      <c r="AB14" s="7" t="n"/>
-      <c r="AC14" s="7" t="n"/>
-      <c r="AD14" s="7" t="n"/>
-      <c r="AE14" s="7" t="n"/>
-      <c r="AF14" s="7" t="n"/>
-      <c r="AG14" s="7" t="n"/>
+      <c r="C14" s="7" t="inlineStr"/>
+      <c r="D14" s="7" t="inlineStr"/>
+      <c r="E14" s="7" t="inlineStr"/>
+      <c r="F14" s="7" t="inlineStr"/>
+      <c r="G14" s="7" t="inlineStr"/>
+      <c r="H14" s="7" t="inlineStr"/>
+      <c r="I14" s="7" t="inlineStr"/>
+      <c r="J14" s="7" t="inlineStr"/>
+      <c r="K14" s="7" t="inlineStr"/>
+      <c r="L14" s="7" t="inlineStr"/>
+      <c r="M14" s="7" t="inlineStr"/>
+      <c r="N14" s="7" t="inlineStr"/>
+      <c r="O14" s="7" t="inlineStr"/>
+      <c r="P14" s="7" t="inlineStr"/>
+      <c r="Q14" s="7" t="inlineStr"/>
+      <c r="R14" s="7" t="inlineStr"/>
+      <c r="S14" s="7" t="inlineStr"/>
+      <c r="T14" s="7" t="inlineStr"/>
+      <c r="U14" s="7" t="inlineStr"/>
+      <c r="V14" s="7" t="inlineStr"/>
+      <c r="W14" s="7" t="inlineStr"/>
+      <c r="X14" s="7" t="inlineStr"/>
+      <c r="Y14" s="7" t="inlineStr"/>
+      <c r="Z14" s="7" t="inlineStr"/>
+      <c r="AA14" s="7" t="inlineStr"/>
+      <c r="AB14" s="7" t="inlineStr"/>
+      <c r="AC14" s="7" t="inlineStr"/>
+      <c r="AD14" s="7" t="inlineStr"/>
+      <c r="AE14" s="7" t="inlineStr"/>
+      <c r="AF14" s="7" t="inlineStr"/>
+      <c r="AG14" s="7" t="inlineStr"/>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="9" t="n">
@@ -2072,37 +2075,37 @@
           <t>อัดจาระบีตามหัวอัดจาระบีทุก ๆ จุด</t>
         </is>
       </c>
-      <c r="C15" s="7" t="n"/>
-      <c r="D15" s="7" t="n"/>
-      <c r="E15" s="7" t="n"/>
-      <c r="F15" s="7" t="n"/>
-      <c r="G15" s="7" t="n"/>
-      <c r="H15" s="7" t="n"/>
-      <c r="I15" s="7" t="n"/>
-      <c r="J15" s="7" t="n"/>
-      <c r="K15" s="7" t="n"/>
-      <c r="L15" s="7" t="n"/>
-      <c r="M15" s="7" t="n"/>
-      <c r="N15" s="7" t="n"/>
-      <c r="O15" s="7" t="n"/>
-      <c r="P15" s="7" t="n"/>
-      <c r="Q15" s="7" t="n"/>
-      <c r="R15" s="7" t="n"/>
-      <c r="S15" s="7" t="n"/>
-      <c r="T15" s="7" t="n"/>
-      <c r="U15" s="7" t="n"/>
-      <c r="V15" s="7" t="n"/>
-      <c r="W15" s="7" t="n"/>
-      <c r="X15" s="7" t="n"/>
-      <c r="Y15" s="7" t="n"/>
-      <c r="Z15" s="7" t="n"/>
-      <c r="AA15" s="7" t="n"/>
-      <c r="AB15" s="7" t="n"/>
-      <c r="AC15" s="7" t="n"/>
-      <c r="AD15" s="7" t="n"/>
-      <c r="AE15" s="7" t="n"/>
-      <c r="AF15" s="7" t="n"/>
-      <c r="AG15" s="7" t="n"/>
+      <c r="C15" s="7" t="inlineStr"/>
+      <c r="D15" s="7" t="inlineStr"/>
+      <c r="E15" s="7" t="inlineStr"/>
+      <c r="F15" s="7" t="inlineStr"/>
+      <c r="G15" s="7" t="inlineStr"/>
+      <c r="H15" s="7" t="inlineStr"/>
+      <c r="I15" s="7" t="inlineStr"/>
+      <c r="J15" s="7" t="inlineStr"/>
+      <c r="K15" s="7" t="inlineStr"/>
+      <c r="L15" s="7" t="inlineStr"/>
+      <c r="M15" s="7" t="inlineStr"/>
+      <c r="N15" s="7" t="inlineStr"/>
+      <c r="O15" s="7" t="inlineStr"/>
+      <c r="P15" s="7" t="inlineStr"/>
+      <c r="Q15" s="7" t="inlineStr"/>
+      <c r="R15" s="7" t="inlineStr"/>
+      <c r="S15" s="7" t="inlineStr"/>
+      <c r="T15" s="7" t="inlineStr"/>
+      <c r="U15" s="7" t="inlineStr"/>
+      <c r="V15" s="7" t="inlineStr"/>
+      <c r="W15" s="7" t="inlineStr"/>
+      <c r="X15" s="7" t="inlineStr"/>
+      <c r="Y15" s="7" t="inlineStr"/>
+      <c r="Z15" s="7" t="inlineStr"/>
+      <c r="AA15" s="7" t="inlineStr"/>
+      <c r="AB15" s="7" t="inlineStr"/>
+      <c r="AC15" s="7" t="inlineStr"/>
+      <c r="AD15" s="7" t="inlineStr"/>
+      <c r="AE15" s="7" t="inlineStr"/>
+      <c r="AF15" s="7" t="inlineStr"/>
+      <c r="AG15" s="7" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="9" t="n">
@@ -2113,72 +2116,72 @@
           <t>ตรวจสอบความพร้อมสภาพโดยรวมของเครื่อง</t>
         </is>
       </c>
-      <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
-      <c r="E16" s="7" t="n"/>
-      <c r="F16" s="7" t="n"/>
-      <c r="G16" s="7" t="n"/>
-      <c r="H16" s="7" t="n"/>
-      <c r="I16" s="7" t="n"/>
-      <c r="J16" s="7" t="n"/>
-      <c r="K16" s="7" t="n"/>
-      <c r="L16" s="7" t="n"/>
-      <c r="M16" s="7" t="n"/>
-      <c r="N16" s="7" t="n"/>
-      <c r="O16" s="7" t="n"/>
-      <c r="P16" s="7" t="n"/>
-      <c r="Q16" s="7" t="n"/>
-      <c r="R16" s="7" t="n"/>
-      <c r="S16" s="7" t="n"/>
-      <c r="T16" s="7" t="n"/>
-      <c r="U16" s="7" t="n"/>
-      <c r="V16" s="7" t="n"/>
-      <c r="W16" s="7" t="n"/>
-      <c r="X16" s="7" t="n"/>
-      <c r="Y16" s="7" t="n"/>
-      <c r="Z16" s="7" t="n"/>
-      <c r="AA16" s="7" t="n"/>
-      <c r="AB16" s="7" t="n"/>
-      <c r="AC16" s="7" t="n"/>
-      <c r="AD16" s="7" t="n"/>
-      <c r="AE16" s="7" t="n"/>
-      <c r="AF16" s="7" t="n"/>
-      <c r="AG16" s="7" t="n"/>
+      <c r="C16" s="7" t="inlineStr"/>
+      <c r="D16" s="7" t="inlineStr"/>
+      <c r="E16" s="7" t="inlineStr"/>
+      <c r="F16" s="7" t="inlineStr"/>
+      <c r="G16" s="7" t="inlineStr"/>
+      <c r="H16" s="7" t="inlineStr"/>
+      <c r="I16" s="7" t="inlineStr"/>
+      <c r="J16" s="7" t="inlineStr"/>
+      <c r="K16" s="7" t="inlineStr"/>
+      <c r="L16" s="7" t="inlineStr"/>
+      <c r="M16" s="7" t="inlineStr"/>
+      <c r="N16" s="7" t="inlineStr"/>
+      <c r="O16" s="7" t="inlineStr"/>
+      <c r="P16" s="7" t="inlineStr"/>
+      <c r="Q16" s="7" t="inlineStr"/>
+      <c r="R16" s="7" t="inlineStr"/>
+      <c r="S16" s="7" t="inlineStr"/>
+      <c r="T16" s="7" t="inlineStr"/>
+      <c r="U16" s="7" t="inlineStr"/>
+      <c r="V16" s="7" t="inlineStr"/>
+      <c r="W16" s="7" t="inlineStr"/>
+      <c r="X16" s="7" t="inlineStr"/>
+      <c r="Y16" s="7" t="inlineStr"/>
+      <c r="Z16" s="7" t="inlineStr"/>
+      <c r="AA16" s="7" t="inlineStr"/>
+      <c r="AB16" s="7" t="inlineStr"/>
+      <c r="AC16" s="7" t="inlineStr"/>
+      <c r="AD16" s="7" t="inlineStr"/>
+      <c r="AE16" s="7" t="inlineStr"/>
+      <c r="AF16" s="7" t="inlineStr"/>
+      <c r="AG16" s="7" t="inlineStr"/>
     </row>
     <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="6" t="n"/>
       <c r="B17" s="5" t="n"/>
-      <c r="C17" s="41" t="n"/>
-      <c r="D17" s="41" t="n"/>
-      <c r="E17" s="41" t="n"/>
-      <c r="F17" s="41" t="n"/>
-      <c r="G17" s="41" t="n"/>
-      <c r="H17" s="41" t="n"/>
-      <c r="I17" s="41" t="n"/>
-      <c r="J17" s="41" t="n"/>
-      <c r="K17" s="41" t="n"/>
-      <c r="L17" s="41" t="n"/>
-      <c r="M17" s="41" t="n"/>
-      <c r="N17" s="41" t="n"/>
-      <c r="O17" s="41" t="n"/>
-      <c r="P17" s="41" t="n"/>
-      <c r="Q17" s="41" t="n"/>
-      <c r="R17" s="41" t="n"/>
-      <c r="S17" s="41" t="n"/>
-      <c r="T17" s="41" t="n"/>
-      <c r="U17" s="41" t="n"/>
-      <c r="V17" s="41" t="n"/>
-      <c r="W17" s="41" t="n"/>
-      <c r="X17" s="41" t="n"/>
-      <c r="Y17" s="41" t="n"/>
-      <c r="Z17" s="41" t="n"/>
-      <c r="AA17" s="41" t="n"/>
-      <c r="AB17" s="41" t="n"/>
-      <c r="AC17" s="41" t="n"/>
-      <c r="AD17" s="41" t="n"/>
-      <c r="AE17" s="41" t="n"/>
-      <c r="AF17" s="41" t="n"/>
-      <c r="AG17" s="41" t="n"/>
+      <c r="C17" s="41" t="inlineStr"/>
+      <c r="D17" s="41" t="inlineStr"/>
+      <c r="E17" s="41" t="inlineStr"/>
+      <c r="F17" s="41" t="inlineStr"/>
+      <c r="G17" s="41" t="inlineStr"/>
+      <c r="H17" s="41" t="inlineStr"/>
+      <c r="I17" s="41" t="inlineStr"/>
+      <c r="J17" s="41" t="inlineStr"/>
+      <c r="K17" s="41" t="inlineStr"/>
+      <c r="L17" s="41" t="inlineStr"/>
+      <c r="M17" s="41" t="inlineStr"/>
+      <c r="N17" s="41" t="inlineStr"/>
+      <c r="O17" s="41" t="inlineStr"/>
+      <c r="P17" s="41" t="inlineStr"/>
+      <c r="Q17" s="41" t="inlineStr"/>
+      <c r="R17" s="41" t="inlineStr"/>
+      <c r="S17" s="41" t="inlineStr"/>
+      <c r="T17" s="41" t="inlineStr"/>
+      <c r="U17" s="41" t="inlineStr"/>
+      <c r="V17" s="41" t="inlineStr"/>
+      <c r="W17" s="41" t="inlineStr"/>
+      <c r="X17" s="41" t="inlineStr"/>
+      <c r="Y17" s="41" t="inlineStr"/>
+      <c r="Z17" s="41" t="inlineStr"/>
+      <c r="AA17" s="41" t="inlineStr"/>
+      <c r="AB17" s="41" t="inlineStr"/>
+      <c r="AC17" s="41" t="inlineStr"/>
+      <c r="AD17" s="41" t="inlineStr"/>
+      <c r="AE17" s="41" t="inlineStr"/>
+      <c r="AF17" s="41" t="inlineStr"/>
+      <c r="AG17" s="41" t="inlineStr"/>
     </row>
     <row r="18" ht="22.5" customHeight="1">
       <c r="B18" s="4" t="n"/>
@@ -2216,37 +2219,37 @@
     </row>
     <row r="19" ht="22.5" customHeight="1">
       <c r="B19" s="4" t="n"/>
-      <c r="C19" s="22" t="n"/>
-      <c r="D19" s="22" t="n"/>
-      <c r="E19" s="22" t="n"/>
-      <c r="F19" s="22" t="n"/>
-      <c r="G19" s="22" t="n"/>
-      <c r="H19" s="22" t="n"/>
-      <c r="I19" s="22" t="n"/>
-      <c r="J19" s="22" t="n"/>
-      <c r="K19" s="22" t="n"/>
-      <c r="L19" s="22" t="n"/>
-      <c r="M19" s="22" t="n"/>
-      <c r="N19" s="22" t="n"/>
-      <c r="O19" s="22" t="n"/>
-      <c r="P19" s="22" t="n"/>
-      <c r="Q19" s="22" t="n"/>
-      <c r="R19" s="22" t="n"/>
-      <c r="S19" s="22" t="n"/>
-      <c r="T19" s="22" t="n"/>
-      <c r="U19" s="22" t="n"/>
-      <c r="V19" s="22" t="n"/>
-      <c r="W19" s="22" t="n"/>
-      <c r="X19" s="22" t="n"/>
-      <c r="Y19" s="22" t="n"/>
-      <c r="Z19" s="22" t="n"/>
-      <c r="AA19" s="22" t="n"/>
-      <c r="AB19" s="22" t="n"/>
-      <c r="AC19" s="22" t="n"/>
-      <c r="AD19" s="22" t="n"/>
-      <c r="AE19" s="22" t="n"/>
-      <c r="AF19" s="22" t="n"/>
-      <c r="AG19" s="22" t="n"/>
+      <c r="C19" s="22" t="inlineStr"/>
+      <c r="D19" s="22" t="inlineStr"/>
+      <c r="E19" s="22" t="inlineStr"/>
+      <c r="F19" s="22" t="inlineStr"/>
+      <c r="G19" s="22" t="inlineStr"/>
+      <c r="H19" s="22" t="inlineStr"/>
+      <c r="I19" s="22" t="inlineStr"/>
+      <c r="J19" s="22" t="inlineStr"/>
+      <c r="K19" s="22" t="inlineStr"/>
+      <c r="L19" s="22" t="inlineStr"/>
+      <c r="M19" s="22" t="inlineStr"/>
+      <c r="N19" s="22" t="inlineStr"/>
+      <c r="O19" s="22" t="inlineStr"/>
+      <c r="P19" s="22" t="inlineStr"/>
+      <c r="Q19" s="22" t="inlineStr"/>
+      <c r="R19" s="22" t="inlineStr"/>
+      <c r="S19" s="22" t="inlineStr"/>
+      <c r="T19" s="22" t="inlineStr"/>
+      <c r="U19" s="22" t="inlineStr"/>
+      <c r="V19" s="22" t="inlineStr"/>
+      <c r="W19" s="22" t="inlineStr"/>
+      <c r="X19" s="22" t="inlineStr"/>
+      <c r="Y19" s="22" t="inlineStr"/>
+      <c r="Z19" s="22" t="inlineStr"/>
+      <c r="AA19" s="22" t="inlineStr"/>
+      <c r="AB19" s="22" t="inlineStr"/>
+      <c r="AC19" s="22" t="inlineStr"/>
+      <c r="AD19" s="22" t="inlineStr"/>
+      <c r="AE19" s="22" t="inlineStr"/>
+      <c r="AF19" s="22" t="inlineStr"/>
+      <c r="AG19" s="22" t="inlineStr"/>
     </row>
     <row r="20" ht="22.5" customHeight="1">
       <c r="B20" s="4" t="n"/>
@@ -2290,7 +2293,7 @@
       </c>
     </row>
     <row r="22" ht="198.75" customHeight="1">
-      <c r="B22" s="34" t="n"/>
+      <c r="B22" s="43" t="inlineStr"/>
     </row>
     <row r="23" ht="23.25" customHeight="1"/>
     <row r="24" ht="23.25" customHeight="1">

--- a/FM-MN-07_LATHE-01.xlsx
+++ b/FM-MN-07_LATHE-01.xlsx
@@ -289,7 +289,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
@@ -395,6 +395,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1706,7 +1715,11 @@
           <t>การ WORM SPINDLE ก่อนเริ่มงาน 15 นาที</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr"/>
+      <c r="C6" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="D6" s="7" t="inlineStr"/>
       <c r="E6" s="7" t="inlineStr"/>
       <c r="F6" s="7" t="inlineStr"/>
@@ -1747,7 +1760,11 @@
           <t>เช็คระดับน้ำมันเครื่องในห้องเกียร์</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr"/>
+      <c r="C7" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="D7" s="7" t="inlineStr"/>
       <c r="E7" s="7" t="inlineStr"/>
       <c r="F7" s="7" t="inlineStr"/>
@@ -1788,7 +1805,11 @@
           <t>เช็คระบบเฟื่องทดลองเปลี่ยนรอบตวามเร็วต่าง ๆ</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr"/>
+      <c r="C8" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="D8" s="7" t="inlineStr"/>
       <c r="E8" s="7" t="inlineStr"/>
       <c r="F8" s="7" t="inlineStr"/>
@@ -1829,7 +1850,11 @@
           <t>เช็ค AUTO แกน X,Y</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr"/>
+      <c r="C9" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="D9" s="7" t="inlineStr"/>
       <c r="E9" s="7" t="inlineStr"/>
       <c r="F9" s="7" t="inlineStr"/>
@@ -1870,7 +1895,11 @@
           <t>เช็คระดับน้ำมันหล่อลื่นใน PUMP</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr"/>
+      <c r="C10" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="D10" s="7" t="inlineStr"/>
       <c r="E10" s="7" t="inlineStr"/>
       <c r="F10" s="7" t="inlineStr"/>
@@ -1911,7 +1940,11 @@
           <t>เช็คน้ำมันหล่อเย็นและการทำงานของปั้ม</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr"/>
+      <c r="C11" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="D11" s="7" t="inlineStr"/>
       <c r="E11" s="7" t="inlineStr"/>
       <c r="F11" s="7" t="inlineStr"/>
@@ -1952,7 +1985,11 @@
           <t>ตรวจสอบหน้าจอ  DIGITAL  READ OUT และการ ทำงานของ  LINEAR  SCALE</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr"/>
+      <c r="C12" s="45" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="D12" s="11" t="inlineStr"/>
       <c r="E12" s="11" t="inlineStr"/>
       <c r="F12" s="11" t="inlineStr"/>
@@ -1993,7 +2030,11 @@
           <t>ตรวจเช็คสภาพและความตึงของสายพาน</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr"/>
+      <c r="C13" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="D13" s="7" t="inlineStr"/>
       <c r="E13" s="7" t="inlineStr"/>
       <c r="F13" s="7" t="inlineStr"/>
@@ -2034,7 +2075,11 @@
           <t>ตรวจสอบการทำงานของไฟฟ้าแสงสว่าง</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr"/>
+      <c r="C14" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="D14" s="7" t="inlineStr"/>
       <c r="E14" s="7" t="inlineStr"/>
       <c r="F14" s="7" t="inlineStr"/>
@@ -2075,7 +2120,11 @@
           <t>อัดจาระบีตามหัวอัดจาระบีทุก ๆ จุด</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr"/>
+      <c r="C15" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="D15" s="7" t="inlineStr"/>
       <c r="E15" s="7" t="inlineStr"/>
       <c r="F15" s="7" t="inlineStr"/>
@@ -2116,7 +2165,11 @@
           <t>ตรวจสอบความพร้อมสภาพโดยรวมของเครื่อง</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr"/>
+      <c r="C16" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="D16" s="7" t="inlineStr"/>
       <c r="E16" s="7" t="inlineStr"/>
       <c r="F16" s="7" t="inlineStr"/>
@@ -2151,7 +2204,11 @@
     <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="6" t="n"/>
       <c r="B17" s="5" t="n"/>
-      <c r="C17" s="41" t="inlineStr"/>
+      <c r="C17" s="46" t="inlineStr">
+        <is>
+          <t>ลุงคอง</t>
+        </is>
+      </c>
       <c r="D17" s="41" t="inlineStr"/>
       <c r="E17" s="41" t="inlineStr"/>
       <c r="F17" s="41" t="inlineStr"/>

--- a/FM-MN-07_LATHE-01.xlsx
+++ b/FM-MN-07_LATHE-01.xlsx
@@ -1721,7 +1721,11 @@
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr"/>
-      <c r="E6" s="7" t="inlineStr"/>
+      <c r="E6" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="F6" s="7" t="inlineStr"/>
       <c r="G6" s="7" t="inlineStr"/>
       <c r="H6" s="7" t="inlineStr"/>
@@ -1766,7 +1770,11 @@
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr"/>
-      <c r="E7" s="7" t="inlineStr"/>
+      <c r="E7" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="F7" s="7" t="inlineStr"/>
       <c r="G7" s="7" t="inlineStr"/>
       <c r="H7" s="7" t="inlineStr"/>
@@ -1811,7 +1819,11 @@
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr"/>
-      <c r="E8" s="7" t="inlineStr"/>
+      <c r="E8" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="F8" s="7" t="inlineStr"/>
       <c r="G8" s="7" t="inlineStr"/>
       <c r="H8" s="7" t="inlineStr"/>
@@ -1856,7 +1868,11 @@
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr"/>
-      <c r="E9" s="7" t="inlineStr"/>
+      <c r="E9" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="F9" s="7" t="inlineStr"/>
       <c r="G9" s="7" t="inlineStr"/>
       <c r="H9" s="7" t="inlineStr"/>
@@ -1901,7 +1917,11 @@
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr"/>
-      <c r="E10" s="7" t="inlineStr"/>
+      <c r="E10" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="F10" s="7" t="inlineStr"/>
       <c r="G10" s="7" t="inlineStr"/>
       <c r="H10" s="7" t="inlineStr"/>
@@ -1946,7 +1966,11 @@
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr"/>
-      <c r="E11" s="7" t="inlineStr"/>
+      <c r="E11" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="F11" s="7" t="inlineStr"/>
       <c r="G11" s="7" t="inlineStr"/>
       <c r="H11" s="7" t="inlineStr"/>
@@ -1991,7 +2015,11 @@
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr"/>
-      <c r="E12" s="11" t="inlineStr"/>
+      <c r="E12" s="45" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="F12" s="11" t="inlineStr"/>
       <c r="G12" s="11" t="inlineStr"/>
       <c r="H12" s="11" t="inlineStr"/>
@@ -2036,7 +2064,11 @@
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr"/>
-      <c r="E13" s="7" t="inlineStr"/>
+      <c r="E13" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="F13" s="7" t="inlineStr"/>
       <c r="G13" s="7" t="inlineStr"/>
       <c r="H13" s="7" t="inlineStr"/>
@@ -2081,7 +2113,11 @@
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr"/>
-      <c r="E14" s="7" t="inlineStr"/>
+      <c r="E14" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="F14" s="7" t="inlineStr"/>
       <c r="G14" s="7" t="inlineStr"/>
       <c r="H14" s="7" t="inlineStr"/>
@@ -2126,7 +2162,11 @@
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr"/>
-      <c r="E15" s="7" t="inlineStr"/>
+      <c r="E15" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="F15" s="7" t="inlineStr"/>
       <c r="G15" s="7" t="inlineStr"/>
       <c r="H15" s="7" t="inlineStr"/>
@@ -2171,7 +2211,11 @@
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr"/>
-      <c r="E16" s="7" t="inlineStr"/>
+      <c r="E16" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="F16" s="7" t="inlineStr"/>
       <c r="G16" s="7" t="inlineStr"/>
       <c r="H16" s="7" t="inlineStr"/>
@@ -2210,7 +2254,11 @@
         </is>
       </c>
       <c r="D17" s="41" t="inlineStr"/>
-      <c r="E17" s="41" t="inlineStr"/>
+      <c r="E17" s="46" t="inlineStr">
+        <is>
+          <t>ขวัญชัย</t>
+        </is>
+      </c>
       <c r="F17" s="41" t="inlineStr"/>
       <c r="G17" s="41" t="inlineStr"/>
       <c r="H17" s="41" t="inlineStr"/>

--- a/FM-MN-07_LATHE-01.xlsx
+++ b/FM-MN-07_LATHE-01.xlsx
@@ -1715,17 +1715,9 @@
           <t>การ WORM SPINDLE ก่อนเริ่มงาน 15 นาที</t>
         </is>
       </c>
-      <c r="C6" s="44" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="C6" s="44" t="inlineStr"/>
       <c r="D6" s="7" t="inlineStr"/>
-      <c r="E6" s="44" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="E6" s="44" t="inlineStr"/>
       <c r="F6" s="7" t="inlineStr"/>
       <c r="G6" s="7" t="inlineStr"/>
       <c r="H6" s="7" t="inlineStr"/>
@@ -1764,17 +1756,9 @@
           <t>เช็คระดับน้ำมันเครื่องในห้องเกียร์</t>
         </is>
       </c>
-      <c r="C7" s="44" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="C7" s="44" t="inlineStr"/>
       <c r="D7" s="7" t="inlineStr"/>
-      <c r="E7" s="44" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="E7" s="44" t="inlineStr"/>
       <c r="F7" s="7" t="inlineStr"/>
       <c r="G7" s="7" t="inlineStr"/>
       <c r="H7" s="7" t="inlineStr"/>
@@ -1813,17 +1797,9 @@
           <t>เช็คระบบเฟื่องทดลองเปลี่ยนรอบตวามเร็วต่าง ๆ</t>
         </is>
       </c>
-      <c r="C8" s="44" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="C8" s="44" t="inlineStr"/>
       <c r="D8" s="7" t="inlineStr"/>
-      <c r="E8" s="44" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="E8" s="44" t="inlineStr"/>
       <c r="F8" s="7" t="inlineStr"/>
       <c r="G8" s="7" t="inlineStr"/>
       <c r="H8" s="7" t="inlineStr"/>
@@ -1862,17 +1838,9 @@
           <t>เช็ค AUTO แกน X,Y</t>
         </is>
       </c>
-      <c r="C9" s="44" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="C9" s="44" t="inlineStr"/>
       <c r="D9" s="7" t="inlineStr"/>
-      <c r="E9" s="44" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="E9" s="44" t="inlineStr"/>
       <c r="F9" s="7" t="inlineStr"/>
       <c r="G9" s="7" t="inlineStr"/>
       <c r="H9" s="7" t="inlineStr"/>
@@ -1911,17 +1879,9 @@
           <t>เช็คระดับน้ำมันหล่อลื่นใน PUMP</t>
         </is>
       </c>
-      <c r="C10" s="44" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="C10" s="44" t="inlineStr"/>
       <c r="D10" s="7" t="inlineStr"/>
-      <c r="E10" s="44" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="E10" s="44" t="inlineStr"/>
       <c r="F10" s="7" t="inlineStr"/>
       <c r="G10" s="7" t="inlineStr"/>
       <c r="H10" s="7" t="inlineStr"/>
@@ -1960,17 +1920,9 @@
           <t>เช็คน้ำมันหล่อเย็นและการทำงานของปั้ม</t>
         </is>
       </c>
-      <c r="C11" s="44" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="C11" s="44" t="inlineStr"/>
       <c r="D11" s="7" t="inlineStr"/>
-      <c r="E11" s="44" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="E11" s="44" t="inlineStr"/>
       <c r="F11" s="7" t="inlineStr"/>
       <c r="G11" s="7" t="inlineStr"/>
       <c r="H11" s="7" t="inlineStr"/>
@@ -2009,17 +1961,9 @@
           <t>ตรวจสอบหน้าจอ  DIGITAL  READ OUT และการ ทำงานของ  LINEAR  SCALE</t>
         </is>
       </c>
-      <c r="C12" s="45" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="C12" s="45" t="inlineStr"/>
       <c r="D12" s="11" t="inlineStr"/>
-      <c r="E12" s="45" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="E12" s="45" t="inlineStr"/>
       <c r="F12" s="11" t="inlineStr"/>
       <c r="G12" s="11" t="inlineStr"/>
       <c r="H12" s="11" t="inlineStr"/>
@@ -2058,17 +2002,9 @@
           <t>ตรวจเช็คสภาพและความตึงของสายพาน</t>
         </is>
       </c>
-      <c r="C13" s="44" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="C13" s="44" t="inlineStr"/>
       <c r="D13" s="7" t="inlineStr"/>
-      <c r="E13" s="44" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="E13" s="44" t="inlineStr"/>
       <c r="F13" s="7" t="inlineStr"/>
       <c r="G13" s="7" t="inlineStr"/>
       <c r="H13" s="7" t="inlineStr"/>
@@ -2107,17 +2043,9 @@
           <t>ตรวจสอบการทำงานของไฟฟ้าแสงสว่าง</t>
         </is>
       </c>
-      <c r="C14" s="44" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="C14" s="44" t="inlineStr"/>
       <c r="D14" s="7" t="inlineStr"/>
-      <c r="E14" s="44" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="E14" s="44" t="inlineStr"/>
       <c r="F14" s="7" t="inlineStr"/>
       <c r="G14" s="7" t="inlineStr"/>
       <c r="H14" s="7" t="inlineStr"/>
@@ -2156,17 +2084,9 @@
           <t>อัดจาระบีตามหัวอัดจาระบีทุก ๆ จุด</t>
         </is>
       </c>
-      <c r="C15" s="44" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="C15" s="44" t="inlineStr"/>
       <c r="D15" s="7" t="inlineStr"/>
-      <c r="E15" s="44" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="E15" s="44" t="inlineStr"/>
       <c r="F15" s="7" t="inlineStr"/>
       <c r="G15" s="7" t="inlineStr"/>
       <c r="H15" s="7" t="inlineStr"/>
@@ -2205,17 +2125,9 @@
           <t>ตรวจสอบความพร้อมสภาพโดยรวมของเครื่อง</t>
         </is>
       </c>
-      <c r="C16" s="44" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="C16" s="44" t="inlineStr"/>
       <c r="D16" s="7" t="inlineStr"/>
-      <c r="E16" s="44" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
+      <c r="E16" s="44" t="inlineStr"/>
       <c r="F16" s="7" t="inlineStr"/>
       <c r="G16" s="7" t="inlineStr"/>
       <c r="H16" s="7" t="inlineStr"/>
@@ -2248,17 +2160,9 @@
     <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="6" t="n"/>
       <c r="B17" s="5" t="n"/>
-      <c r="C17" s="46" t="inlineStr">
-        <is>
-          <t>ลุงคอง</t>
-        </is>
-      </c>
+      <c r="C17" s="46" t="inlineStr"/>
       <c r="D17" s="41" t="inlineStr"/>
-      <c r="E17" s="46" t="inlineStr">
-        <is>
-          <t>ขวัญชัย</t>
-        </is>
-      </c>
+      <c r="E17" s="46" t="inlineStr"/>
       <c r="F17" s="41" t="inlineStr"/>
       <c r="G17" s="41" t="inlineStr"/>
       <c r="H17" s="41" t="inlineStr"/>

--- a/FM-MN-07_LATHE-01.xlsx
+++ b/FM-MN-07_LATHE-01.xlsx
@@ -1720,7 +1720,11 @@
       <c r="E6" s="44" t="inlineStr"/>
       <c r="F6" s="7" t="inlineStr"/>
       <c r="G6" s="7" t="inlineStr"/>
-      <c r="H6" s="7" t="inlineStr"/>
+      <c r="H6" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I6" s="7" t="inlineStr"/>
       <c r="J6" s="7" t="inlineStr"/>
       <c r="K6" s="7" t="inlineStr"/>
@@ -1761,7 +1765,11 @@
       <c r="E7" s="44" t="inlineStr"/>
       <c r="F7" s="7" t="inlineStr"/>
       <c r="G7" s="7" t="inlineStr"/>
-      <c r="H7" s="7" t="inlineStr"/>
+      <c r="H7" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I7" s="7" t="inlineStr"/>
       <c r="J7" s="7" t="inlineStr"/>
       <c r="K7" s="7" t="inlineStr"/>
@@ -1802,7 +1810,11 @@
       <c r="E8" s="44" t="inlineStr"/>
       <c r="F8" s="7" t="inlineStr"/>
       <c r="G8" s="7" t="inlineStr"/>
-      <c r="H8" s="7" t="inlineStr"/>
+      <c r="H8" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I8" s="7" t="inlineStr"/>
       <c r="J8" s="7" t="inlineStr"/>
       <c r="K8" s="7" t="inlineStr"/>
@@ -1843,7 +1855,11 @@
       <c r="E9" s="44" t="inlineStr"/>
       <c r="F9" s="7" t="inlineStr"/>
       <c r="G9" s="7" t="inlineStr"/>
-      <c r="H9" s="7" t="inlineStr"/>
+      <c r="H9" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I9" s="7" t="inlineStr"/>
       <c r="J9" s="7" t="inlineStr"/>
       <c r="K9" s="7" t="inlineStr"/>
@@ -1884,7 +1900,11 @@
       <c r="E10" s="44" t="inlineStr"/>
       <c r="F10" s="7" t="inlineStr"/>
       <c r="G10" s="7" t="inlineStr"/>
-      <c r="H10" s="7" t="inlineStr"/>
+      <c r="H10" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I10" s="7" t="inlineStr"/>
       <c r="J10" s="7" t="inlineStr"/>
       <c r="K10" s="7" t="inlineStr"/>
@@ -1925,7 +1945,11 @@
       <c r="E11" s="44" t="inlineStr"/>
       <c r="F11" s="7" t="inlineStr"/>
       <c r="G11" s="7" t="inlineStr"/>
-      <c r="H11" s="7" t="inlineStr"/>
+      <c r="H11" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I11" s="7" t="inlineStr"/>
       <c r="J11" s="7" t="inlineStr"/>
       <c r="K11" s="7" t="inlineStr"/>
@@ -1966,7 +1990,11 @@
       <c r="E12" s="45" t="inlineStr"/>
       <c r="F12" s="11" t="inlineStr"/>
       <c r="G12" s="11" t="inlineStr"/>
-      <c r="H12" s="11" t="inlineStr"/>
+      <c r="H12" s="45" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I12" s="11" t="inlineStr"/>
       <c r="J12" s="11" t="inlineStr"/>
       <c r="K12" s="11" t="inlineStr"/>
@@ -2007,7 +2035,11 @@
       <c r="E13" s="44" t="inlineStr"/>
       <c r="F13" s="7" t="inlineStr"/>
       <c r="G13" s="7" t="inlineStr"/>
-      <c r="H13" s="7" t="inlineStr"/>
+      <c r="H13" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I13" s="7" t="inlineStr"/>
       <c r="J13" s="7" t="inlineStr"/>
       <c r="K13" s="7" t="inlineStr"/>
@@ -2048,7 +2080,11 @@
       <c r="E14" s="44" t="inlineStr"/>
       <c r="F14" s="7" t="inlineStr"/>
       <c r="G14" s="7" t="inlineStr"/>
-      <c r="H14" s="7" t="inlineStr"/>
+      <c r="H14" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I14" s="7" t="inlineStr"/>
       <c r="J14" s="7" t="inlineStr"/>
       <c r="K14" s="7" t="inlineStr"/>
@@ -2089,7 +2125,11 @@
       <c r="E15" s="44" t="inlineStr"/>
       <c r="F15" s="7" t="inlineStr"/>
       <c r="G15" s="7" t="inlineStr"/>
-      <c r="H15" s="7" t="inlineStr"/>
+      <c r="H15" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I15" s="7" t="inlineStr"/>
       <c r="J15" s="7" t="inlineStr"/>
       <c r="K15" s="7" t="inlineStr"/>
@@ -2130,7 +2170,11 @@
       <c r="E16" s="44" t="inlineStr"/>
       <c r="F16" s="7" t="inlineStr"/>
       <c r="G16" s="7" t="inlineStr"/>
-      <c r="H16" s="7" t="inlineStr"/>
+      <c r="H16" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I16" s="7" t="inlineStr"/>
       <c r="J16" s="7" t="inlineStr"/>
       <c r="K16" s="7" t="inlineStr"/>
@@ -2165,7 +2209,11 @@
       <c r="E17" s="46" t="inlineStr"/>
       <c r="F17" s="41" t="inlineStr"/>
       <c r="G17" s="41" t="inlineStr"/>
-      <c r="H17" s="41" t="inlineStr"/>
+      <c r="H17" s="46" t="inlineStr">
+        <is>
+          <t>ลุงคอง</t>
+        </is>
+      </c>
       <c r="I17" s="41" t="inlineStr"/>
       <c r="J17" s="41" t="inlineStr"/>
       <c r="K17" s="41" t="inlineStr"/>

--- a/FM-MN-07_LATHE-01.xlsx
+++ b/FM-MN-07_LATHE-01.xlsx
@@ -1725,7 +1725,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr"/>
+      <c r="I6" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J6" s="7" t="inlineStr"/>
       <c r="K6" s="7" t="inlineStr"/>
       <c r="L6" s="7" t="inlineStr"/>
@@ -1770,7 +1774,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr"/>
+      <c r="I7" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J7" s="7" t="inlineStr"/>
       <c r="K7" s="7" t="inlineStr"/>
       <c r="L7" s="7" t="inlineStr"/>
@@ -1815,7 +1823,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I8" s="7" t="inlineStr"/>
+      <c r="I8" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J8" s="7" t="inlineStr"/>
       <c r="K8" s="7" t="inlineStr"/>
       <c r="L8" s="7" t="inlineStr"/>
@@ -1860,7 +1872,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr"/>
+      <c r="I9" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J9" s="7" t="inlineStr"/>
       <c r="K9" s="7" t="inlineStr"/>
       <c r="L9" s="7" t="inlineStr"/>
@@ -1905,7 +1921,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I10" s="7" t="inlineStr"/>
+      <c r="I10" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J10" s="7" t="inlineStr"/>
       <c r="K10" s="7" t="inlineStr"/>
       <c r="L10" s="7" t="inlineStr"/>
@@ -1950,7 +1970,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr"/>
+      <c r="I11" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J11" s="7" t="inlineStr"/>
       <c r="K11" s="7" t="inlineStr"/>
       <c r="L11" s="7" t="inlineStr"/>
@@ -1995,7 +2019,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I12" s="11" t="inlineStr"/>
+      <c r="I12" s="45" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J12" s="11" t="inlineStr"/>
       <c r="K12" s="11" t="inlineStr"/>
       <c r="L12" s="11" t="inlineStr"/>
@@ -2040,7 +2068,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I13" s="7" t="inlineStr"/>
+      <c r="I13" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J13" s="7" t="inlineStr"/>
       <c r="K13" s="7" t="inlineStr"/>
       <c r="L13" s="7" t="inlineStr"/>
@@ -2085,7 +2117,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr"/>
+      <c r="I14" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J14" s="7" t="inlineStr"/>
       <c r="K14" s="7" t="inlineStr"/>
       <c r="L14" s="7" t="inlineStr"/>
@@ -2130,7 +2166,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I15" s="7" t="inlineStr"/>
+      <c r="I15" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J15" s="7" t="inlineStr"/>
       <c r="K15" s="7" t="inlineStr"/>
       <c r="L15" s="7" t="inlineStr"/>
@@ -2175,7 +2215,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I16" s="7" t="inlineStr"/>
+      <c r="I16" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J16" s="7" t="inlineStr"/>
       <c r="K16" s="7" t="inlineStr"/>
       <c r="L16" s="7" t="inlineStr"/>
@@ -2214,7 +2258,11 @@
           <t>ลุงคอง</t>
         </is>
       </c>
-      <c r="I17" s="41" t="inlineStr"/>
+      <c r="I17" s="46" t="inlineStr">
+        <is>
+          <t>ลุงคอง</t>
+        </is>
+      </c>
       <c r="J17" s="41" t="inlineStr"/>
       <c r="K17" s="41" t="inlineStr"/>
       <c r="L17" s="41" t="inlineStr"/>

--- a/FM-MN-07_LATHE-01.xlsx
+++ b/FM-MN-07_LATHE-01.xlsx
@@ -289,7 +289,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
@@ -403,6 +403,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
   </cellXfs>
@@ -2330,7 +2333,11 @@
       <c r="F19" s="22" t="inlineStr"/>
       <c r="G19" s="22" t="inlineStr"/>
       <c r="H19" s="22" t="inlineStr"/>
-      <c r="I19" s="22" t="inlineStr"/>
+      <c r="I19" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">วรพจน์ </t>
+        </is>
+      </c>
       <c r="J19" s="22" t="inlineStr"/>
       <c r="K19" s="22" t="inlineStr"/>
       <c r="L19" s="22" t="inlineStr"/>

--- a/FM-MN-07_LATHE-01.xlsx
+++ b/FM-MN-07_LATHE-01.xlsx
@@ -1733,7 +1733,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J6" s="7" t="inlineStr"/>
+      <c r="J6" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K6" s="7" t="inlineStr"/>
       <c r="L6" s="7" t="inlineStr"/>
       <c r="M6" s="7" t="inlineStr"/>
@@ -1782,7 +1786,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J7" s="7" t="inlineStr"/>
+      <c r="J7" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K7" s="7" t="inlineStr"/>
       <c r="L7" s="7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
@@ -1831,7 +1839,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J8" s="7" t="inlineStr"/>
+      <c r="J8" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K8" s="7" t="inlineStr"/>
       <c r="L8" s="7" t="inlineStr"/>
       <c r="M8" s="7" t="inlineStr"/>
@@ -1880,7 +1892,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J9" s="7" t="inlineStr"/>
+      <c r="J9" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K9" s="7" t="inlineStr"/>
       <c r="L9" s="7" t="inlineStr"/>
       <c r="M9" s="7" t="inlineStr"/>
@@ -1929,7 +1945,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J10" s="7" t="inlineStr"/>
+      <c r="J10" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K10" s="7" t="inlineStr"/>
       <c r="L10" s="7" t="inlineStr"/>
       <c r="M10" s="7" t="inlineStr"/>
@@ -1978,7 +1998,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J11" s="7" t="inlineStr"/>
+      <c r="J11" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K11" s="7" t="inlineStr"/>
       <c r="L11" s="7" t="inlineStr"/>
       <c r="M11" s="7" t="inlineStr"/>
@@ -2027,7 +2051,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J12" s="11" t="inlineStr"/>
+      <c r="J12" s="45" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K12" s="11" t="inlineStr"/>
       <c r="L12" s="11" t="inlineStr"/>
       <c r="M12" s="11" t="inlineStr"/>
@@ -2076,7 +2104,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J13" s="7" t="inlineStr"/>
+      <c r="J13" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K13" s="7" t="inlineStr"/>
       <c r="L13" s="7" t="inlineStr"/>
       <c r="M13" s="7" t="inlineStr"/>
@@ -2125,7 +2157,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J14" s="7" t="inlineStr"/>
+      <c r="J14" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K14" s="7" t="inlineStr"/>
       <c r="L14" s="7" t="inlineStr"/>
       <c r="M14" s="7" t="inlineStr"/>
@@ -2174,7 +2210,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J15" s="7" t="inlineStr"/>
+      <c r="J15" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K15" s="7" t="inlineStr"/>
       <c r="L15" s="7" t="inlineStr"/>
       <c r="M15" s="7" t="inlineStr"/>
@@ -2223,7 +2263,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J16" s="7" t="inlineStr"/>
+      <c r="J16" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K16" s="7" t="inlineStr"/>
       <c r="L16" s="7" t="inlineStr"/>
       <c r="M16" s="7" t="inlineStr"/>
@@ -2266,7 +2310,11 @@
           <t>ลุงคอง</t>
         </is>
       </c>
-      <c r="J17" s="41" t="inlineStr"/>
+      <c r="J17" s="46" t="inlineStr">
+        <is>
+          <t>ลุงคอง</t>
+        </is>
+      </c>
       <c r="K17" s="41" t="inlineStr"/>
       <c r="L17" s="41" t="inlineStr"/>
       <c r="M17" s="41" t="inlineStr"/>

--- a/FM-MN-07_LATHE-01.xlsx
+++ b/FM-MN-07_LATHE-01.xlsx
@@ -1739,7 +1739,11 @@
         </is>
       </c>
       <c r="K6" s="7" t="inlineStr"/>
-      <c r="L6" s="7" t="inlineStr"/>
+      <c r="L6" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M6" s="7" t="inlineStr"/>
       <c r="N6" s="7" t="inlineStr"/>
       <c r="O6" s="7" t="inlineStr"/>
@@ -1792,7 +1796,11 @@
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr"/>
-      <c r="L7" s="7" t="inlineStr"/>
+      <c r="L7" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M7" s="7" t="inlineStr"/>
       <c r="N7" s="7" t="inlineStr"/>
       <c r="O7" s="7" t="inlineStr"/>
@@ -1845,7 +1853,11 @@
         </is>
       </c>
       <c r="K8" s="7" t="inlineStr"/>
-      <c r="L8" s="7" t="inlineStr"/>
+      <c r="L8" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M8" s="7" t="inlineStr"/>
       <c r="N8" s="7" t="inlineStr"/>
       <c r="O8" s="7" t="inlineStr"/>
@@ -1898,7 +1910,11 @@
         </is>
       </c>
       <c r="K9" s="7" t="inlineStr"/>
-      <c r="L9" s="7" t="inlineStr"/>
+      <c r="L9" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M9" s="7" t="inlineStr"/>
       <c r="N9" s="7" t="inlineStr"/>
       <c r="O9" s="7" t="inlineStr"/>
@@ -1951,7 +1967,11 @@
         </is>
       </c>
       <c r="K10" s="7" t="inlineStr"/>
-      <c r="L10" s="7" t="inlineStr"/>
+      <c r="L10" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M10" s="7" t="inlineStr"/>
       <c r="N10" s="7" t="inlineStr"/>
       <c r="O10" s="7" t="inlineStr"/>
@@ -2004,7 +2024,11 @@
         </is>
       </c>
       <c r="K11" s="7" t="inlineStr"/>
-      <c r="L11" s="7" t="inlineStr"/>
+      <c r="L11" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M11" s="7" t="inlineStr"/>
       <c r="N11" s="7" t="inlineStr"/>
       <c r="O11" s="7" t="inlineStr"/>
@@ -2057,7 +2081,11 @@
         </is>
       </c>
       <c r="K12" s="11" t="inlineStr"/>
-      <c r="L12" s="11" t="inlineStr"/>
+      <c r="L12" s="45" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M12" s="11" t="inlineStr"/>
       <c r="N12" s="11" t="inlineStr"/>
       <c r="O12" s="11" t="inlineStr"/>
@@ -2110,7 +2138,11 @@
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr"/>
-      <c r="L13" s="7" t="inlineStr"/>
+      <c r="L13" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M13" s="7" t="inlineStr"/>
       <c r="N13" s="7" t="inlineStr"/>
       <c r="O13" s="7" t="inlineStr"/>
@@ -2163,7 +2195,11 @@
         </is>
       </c>
       <c r="K14" s="7" t="inlineStr"/>
-      <c r="L14" s="7" t="inlineStr"/>
+      <c r="L14" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M14" s="7" t="inlineStr"/>
       <c r="N14" s="7" t="inlineStr"/>
       <c r="O14" s="7" t="inlineStr"/>
@@ -2216,7 +2252,11 @@
         </is>
       </c>
       <c r="K15" s="7" t="inlineStr"/>
-      <c r="L15" s="7" t="inlineStr"/>
+      <c r="L15" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M15" s="7" t="inlineStr"/>
       <c r="N15" s="7" t="inlineStr"/>
       <c r="O15" s="7" t="inlineStr"/>
@@ -2269,7 +2309,11 @@
         </is>
       </c>
       <c r="K16" s="7" t="inlineStr"/>
-      <c r="L16" s="7" t="inlineStr"/>
+      <c r="L16" s="44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M16" s="7" t="inlineStr"/>
       <c r="N16" s="7" t="inlineStr"/>
       <c r="O16" s="7" t="inlineStr"/>
@@ -2316,7 +2360,11 @@
         </is>
       </c>
       <c r="K17" s="41" t="inlineStr"/>
-      <c r="L17" s="41" t="inlineStr"/>
+      <c r="L17" s="46" t="inlineStr">
+        <is>
+          <t>ลุงคอง</t>
+        </is>
+      </c>
       <c r="M17" s="41" t="inlineStr"/>
       <c r="N17" s="41" t="inlineStr"/>
       <c r="O17" s="41" t="inlineStr"/>
